--- a/src/attributions/attributions_saliency_traj_119.xlsx
+++ b/src/attributions/attributions_saliency_traj_119.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.04754865169525146</v>
+        <v>0.0004318731953389943</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1162677258253098</v>
+        <v>4.65537013951689e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2629450261592865</v>
+        <v>0.0001905425306176767</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09316883981227875</v>
+        <v>0.0001227248285431415</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1666180640459061</v>
+        <v>0.0001545519917272031</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1342809796333313</v>
+        <v>5.601044904324226e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05069919675588608</v>
+        <v>3.879657742800191e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04508233070373535</v>
+        <v>2.717413008213043e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1885255873203278</v>
+        <v>2.840396155079361e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1733875572681427</v>
+        <v>0.0004263853188604116</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08963055908679962</v>
+        <v>2.153658351744525e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1959518194198608</v>
+        <v>0.0001355702406726778</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01677381619811058</v>
+        <v>0.0001022255455609411</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2001842558383942</v>
+        <v>0.0001765224151313305</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04718830436468124</v>
+        <v>1.396745210513473e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0006602257490158081</v>
+        <v>5.557505937758833e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02422178909182549</v>
+        <v>3.21584775520023e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3006877303123474</v>
+        <v>1.982396861421876e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006682122126221657</v>
+        <v>8.430014713667333e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04771080613136292</v>
+        <v>6.971631955821067e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0409688726067543</v>
+        <v>4.734492540592328e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05788920074701309</v>
+        <v>4.2453011701582e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02329583093523979</v>
+        <v>4.828166856896132e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04894679039716721</v>
+        <v>5.918760507483967e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001889018807560205</v>
+        <v>2.291038254043087e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0464017316699028</v>
+        <v>5.301187411532737e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.05034486576914787</v>
+        <v>1.907706064230297e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04527433589100838</v>
+        <v>9.509433311905013e-07</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05651211366057396</v>
+        <v>4.787681064044591e-06</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0003961268812417984</v>
+        <v>1.089819761546096e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.03314660862088203</v>
+        <v>0.0001645159645704553</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1183149591088295</v>
+        <v>0.0001441554923076183</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.05228754132986069</v>
+        <v>0.0001974188926396891</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.05448202416300774</v>
+        <v>2.669448622327764e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.03773347660899162</v>
+        <v>4.511984661803581e-05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09092381596565247</v>
+        <v>1.461794545321027e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.03903386741876602</v>
+        <v>2.217970722995233e-05</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0442546010017395</v>
+        <v>0.0001193379575852305</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.001630263403058052</v>
+        <v>0.0001029814884532243</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.09213171899318695</v>
+        <v>0.0001281521399505436</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.01623392105102539</v>
+        <v>2.064641012111679e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.003496636170893908</v>
+        <v>2.620906343508977e-06</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.04592509940266609</v>
+        <v>6.760015821782872e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.02860911190509796</v>
+        <v>4.418639946379699e-05</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.04315558075904846</v>
+        <v>2.349625719944015e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.02667295560240746</v>
+        <v>0.0002038810489466414</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.05824218317866325</v>
+        <v>6.559047324117273e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.05841673910617828</v>
+        <v>4.665591768571176e-05</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.05538565665483475</v>
+        <v>8.98973667062819e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.03233282640576363</v>
+        <v>0.0001132465549744666</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.03189224004745483</v>
+        <v>7.16420981916599e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.08209652453660965</v>
+        <v>3.777493111556396e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.08694314956665039</v>
+        <v>1.439765856048325e-05</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1285299807786942</v>
+        <v>4.240280759404413e-05</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.01547306403517723</v>
+        <v>0.0001224227453349158</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1198792159557343</v>
+        <v>2.1715386537835e-06</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1310833543539047</v>
+        <v>9.380037954542786e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.09440194070339203</v>
+        <v>7.914340676506981e-05</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1530030220746994</v>
+        <v>0.0001403609057888389</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1432952433824539</v>
+        <v>1.105928276956547e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.005630210041999817</v>
+        <v>4.325123882154003e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.04489500820636749</v>
+        <v>6.182942161103711e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.2306619584560394</v>
+        <v>5.681544644176029e-05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01919778808951378</v>
+        <v>0.0001470835122745484</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.07085996121168137</v>
+        <v>7.09216546965763e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01918434351682663</v>
+        <v>2.649659654707648e-05</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.05631889402866364</v>
+        <v>3.910042505594902e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.04070849344134331</v>
+        <v>3.859140633721836e-05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.03504061326384544</v>
+        <v>2.424510057608131e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.01628545112907887</v>
+        <v>1.563825207995251e-05</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.02692192792892456</v>
+        <v>3.813497414739686e-06</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.07381186634302139</v>
+        <v>1.771505776559934e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.05433351546525955</v>
+        <v>6.027217750670388e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.07006697356700897</v>
+        <v>4.465100209927186e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.002319201827049255</v>
+        <v>0.0001315171975875273</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.008556464686989784</v>
+        <v>1.316556677011249e-06</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.05073067918419838</v>
+        <v>9.470964141655713e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0324198454618454</v>
+        <v>2.768533158814535e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.02816189825534821</v>
+        <v>2.140188007615507e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.05767560377717018</v>
+        <v>7.776723214192316e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1021875813603401</v>
+        <v>6.163233774714172e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0214531198143959</v>
+        <v>0.0001056165783666074</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.01664005964994431</v>
+        <v>1.128005078498973e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.04445897042751312</v>
+        <v>3.004484460689127e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.03903764858841896</v>
+        <v>2.768783815554343e-05</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01321196835488081</v>
+        <v>4.429035925568314e-06</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.008339513093233109</v>
+        <v>4.990561592421727e-06</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.002154194284230471</v>
+        <v>4.16430011682678e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0270842406898737</v>
+        <v>1.796612195903435e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.03055536933243275</v>
+        <v>8.593881830165628e-06</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.03504546731710434</v>
+        <v>7.457504398189485e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.06239284947514534</v>
+        <v>0.0001423917419742793</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.003917680121958256</v>
+        <v>7.677921530557796e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1148447021842003</v>
+        <v>5.557818440138362e-06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0395040474832058</v>
+        <v>0.0001201013656100258</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.009407801553606987</v>
+        <v>7.986586570041254e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.01095785945653915</v>
+        <v>8.164354221662506e-05</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.01352925226092339</v>
+        <v>5.260652687866241e-05</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.01507287286221981</v>
+        <v>2.12676495721098e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.01820493116974831</v>
+        <v>9.092443360714242e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.01711305789649487</v>
+        <v>4.661042476072907e-05</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.04108504951000214</v>
+        <v>5.135172250447795e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0452314019203186</v>
+        <v>4.221051858621649e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.005426919087767601</v>
+        <v>4.419182732817717e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.03765591233968735</v>
+        <v>6.329355073830811e-06</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0004104666877537966</v>
+        <v>2.247560769319534e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.007245218846946955</v>
+        <v>9.200082331517478e-07</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.04112048074603081</v>
+        <v>8.318818800034933e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.00915967021137476</v>
+        <v>8.482239354634658e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.03593648597598076</v>
+        <v>0.0003813428629655391</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1217673122882843</v>
+        <v>5.437448999146e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.06430442631244659</v>
+        <v>0.0001861193450167775</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06865383684635162</v>
+        <v>8.664031338412315e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.09186157584190369</v>
+        <v>0.0001969768927665427</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.06005822867155075</v>
+        <v>7.381364412140101e-05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07419274747371674</v>
+        <v>9.981134644476697e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.09031921625137329</v>
+        <v>6.403405132004991e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.01898711547255516</v>
+        <v>9.694442269392312e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.04146139696240425</v>
+        <v>6.623173248954117e-05</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.004441248252987862</v>
+        <v>9.153441351372749e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.05879822373390198</v>
+        <v>5.348429112927988e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1335482001304626</v>
+        <v>0.0001320917654084042</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.05529892444610596</v>
+        <v>2.032893826253712e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1185916364192963</v>
+        <v>6.488058716058731e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.06188273057341576</v>
+        <v>6.232567102415487e-05</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.04960087314248085</v>
+        <v>2.008430328714894e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.008149353787302971</v>
+        <v>2.084373772959225e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.02159641496837139</v>
+        <v>3.023115277756006e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.004832022823393345</v>
+        <v>0.0001913942978717387</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.05658077821135521</v>
+        <v>5.268654058454558e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.07533159852027893</v>
+        <v>0.0001742543827276677</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.05017789453268051</v>
+        <v>2.985245373565704e-05</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0220078993588686</v>
+        <v>5.346643229131587e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.04666971415281296</v>
+        <v>6.458511052187532e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.01418940722942352</v>
+        <v>5.803621024824679e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.02758815512061119</v>
+        <v>0.0001310791267314926</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.007829619571566582</v>
+        <v>3.855605609714985e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.07318636029958725</v>
+        <v>1.819319095375249e-06</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.03927720338106155</v>
+        <v>4.766078927787021e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.008840324357151985</v>
+        <v>6.830174243077636e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1036547720432281</v>
+        <v>1.574329871800728e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.008741150610148907</v>
+        <v>3.76813804905396e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.003021888434886932</v>
+        <v>9.260664228349924e-06</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.06964485347270966</v>
+        <v>2.770484388747718e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.04116971790790558</v>
+        <v>7.351867679972202e-05</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.002985518425703049</v>
+        <v>8.402822277275845e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.03299105167388916</v>
+        <v>1.282099583477248e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.01234283857047558</v>
+        <v>4.64553113488364e-06</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.04909888654947281</v>
+        <v>5.217367288423702e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01955380663275719</v>
+        <v>9.254269389202818e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.04144784435629845</v>
+        <v>4.318227001931518e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.07598321884870529</v>
+        <v>3.050375926250126e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.07639749348163605</v>
+        <v>6.456529081333429e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02367603220045567</v>
+        <v>8.418984361924231e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.01224615145474672</v>
+        <v>7.317341805901378e-05</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.04656770825386047</v>
+        <v>5.296014569466934e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.05865002050995827</v>
+        <v>1.721415719657671e-05</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0004982114769518375</v>
+        <v>3.431921504670754e-05</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.03809848055243492</v>
+        <v>3.778652171604335e-05</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.01358016021549702</v>
+        <v>4.953271491103806e-05</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.01958546787500381</v>
+        <v>7.83960786066018e-06</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.04016574844717979</v>
+        <v>7.589265806018375e-06</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.007561067119240761</v>
+        <v>0.0001640439732000232</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.02798346057534218</v>
+        <v>5.128276825416833e-05</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03140166401863098</v>
+        <v>3.515295247780159e-05</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.003066850826144218</v>
+        <v>1.697764855634887e-05</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.01613898761570454</v>
+        <v>4.59850016341079e-05</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.008451962843537331</v>
+        <v>9.604023216525093e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.06579597294330597</v>
+        <v>2.723557372519281e-05</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.008306082338094711</v>
+        <v>1.352279832644854e-05</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.05499821901321411</v>
+        <v>1.706660259515047e-05</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.03274104744195938</v>
+        <v>7.672337960684672e-05</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.009991588070988655</v>
+        <v>7.921479846118018e-05</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.001273086294531822</v>
+        <v>0.0001809870445868</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.1398913860321045</v>
+        <v>0.0003326580626890063</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.05108447372913361</v>
+        <v>5.811061782878824e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.02939286828041077</v>
+        <v>2.615625999169424e-05</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.04311265796422958</v>
+        <v>1.747482201608364e-05</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.05066953226923943</v>
+        <v>3.413929789530812e-06</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.02849035896360874</v>
+        <v>3.395686462681624e-06</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.0135041456669569</v>
+        <v>0.0001531609450466931</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.00701805017888546</v>
+        <v>2.876180587918498e-05</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.006755460053682327</v>
+        <v>7.217027814476751e-06</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.008571762591600418</v>
+        <v>6.395067430275958e-06</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.005457504652440548</v>
+        <v>0.0002253324055345729</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.07677275687456131</v>
+        <v>3.733227003976936e-06</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.04788729175925255</v>
+        <v>4.801446630153805e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.0181653555482626</v>
+        <v>0.0002241414331365377</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.04425964504480362</v>
+        <v>2.77971375908237e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0001054089952958748</v>
+        <v>0.0001473824522690848</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0005269109969958663</v>
+        <v>0.006702683866024017</v>
       </c>
       <c r="C4" t="n">
-        <v>3.229772119084373e-05</v>
+        <v>0.0007038680487312376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002758476766757667</v>
+        <v>0.00561894103884697</v>
       </c>
       <c r="E4" t="n">
-        <v>6.357562961056828e-05</v>
+        <v>0.00164713547565043</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001601596595719457</v>
+        <v>0.001746723311953247</v>
       </c>
       <c r="G4" t="n">
-        <v>4.647481546271592e-07</v>
+        <v>0.001773802796378732</v>
       </c>
       <c r="H4" t="n">
-        <v>3.144330548821017e-05</v>
+        <v>0.001334981294348836</v>
       </c>
       <c r="I4" t="n">
-        <v>2.851825956895482e-05</v>
+        <v>0.0002232003898825496</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001166026922874153</v>
+        <v>0.0006275992491282523</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003465548506937921</v>
+        <v>0.007001610472798347</v>
       </c>
       <c r="L4" t="n">
-        <v>4.890445779892616e-05</v>
+        <v>0.001439728890545666</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002166703634429723</v>
+        <v>0.007509146351367235</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001100976660382003</v>
+        <v>0.00262930104508996</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001920261129271239</v>
+        <v>0.000810349709354341</v>
       </c>
       <c r="P4" t="n">
-        <v>4.561497189570218e-05</v>
+        <v>0.002020402578637004</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001132530742324889</v>
+        <v>0.0001049968996085227</v>
       </c>
       <c r="R4" t="n">
-        <v>2.435248097754084e-05</v>
+        <v>5.304260412231088e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>4.514085503615206e-06</v>
+        <v>1.647948374738917e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>7.111611193977296e-05</v>
+        <v>0.0001736563863232732</v>
       </c>
       <c r="U4" t="n">
-        <v>5.442157089419197e-07</v>
+        <v>0.0003477245045360178</v>
       </c>
       <c r="V4" t="n">
-        <v>4.163276753388345e-05</v>
+        <v>7.458429899998009e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.24211337606539e-05</v>
+        <v>0.0005077232490293682</v>
       </c>
       <c r="X4" t="n">
-        <v>6.254809704842046e-05</v>
+        <v>0.0008680216269567609</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.382523083128035e-05</v>
+        <v>0.0006428058841265738</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.443630728521384e-05</v>
+        <v>0.0009223573142662644</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.720887641771697e-05</v>
+        <v>0.001161242951638997</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.458629751345143e-05</v>
+        <v>0.0001547011197544634</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.727214688202366e-05</v>
+        <v>0.0004586286377161741</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.601869164209347e-05</v>
+        <v>0.0001633536594454199</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.332702544867061e-05</v>
+        <v>0.001438558450900018</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.303396781324409e-05</v>
+        <v>0.0001508138229837641</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.498326259432361e-05</v>
+        <v>0.0008736071176826954</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.119399141520262e-05</v>
+        <v>0.0007555619813501835</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.442506411171053e-05</v>
+        <v>0.0001952128077391535</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.528857243712991e-05</v>
+        <v>0.0002128649794030935</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.226617602398619e-05</v>
+        <v>0.00020963630231563</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.848459113622084e-05</v>
+        <v>0.00178237515501678</v>
       </c>
       <c r="AM4" t="n">
-        <v>9.217495971824974e-06</v>
+        <v>0.0005624947953037918</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.695325050211977e-06</v>
+        <v>0.001037484966218472</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.014875685243169e-06</v>
+        <v>0.0008192601962946355</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.512549589388072e-05</v>
+        <v>0.001163013628683984</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.124525028397329e-05</v>
+        <v>0.000387858017347753</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.166443871625233e-05</v>
+        <v>0.0005684612551704049</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.474445475148968e-05</v>
+        <v>0.0002659345045685768</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.102393020526506e-05</v>
+        <v>0.0001523211976746097</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0003698987129610032</v>
+        <v>0.004043994471430779</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.240287802938838e-06</v>
+        <v>0.0003517685981933028</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0001127414871007204</v>
+        <v>0.002627078210934997</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.181479355087504e-05</v>
+        <v>0.003550939727574587</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.061282303766347e-06</v>
+        <v>0.0006066697533242404</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.027378988917917e-05</v>
+        <v>0.0001313391549047083</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.683937054825947e-05</v>
+        <v>0.0006138228345662355</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.570092566311359e-05</v>
+        <v>0.0004519128706306219</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.316321378108114e-05</v>
+        <v>0.0004487851983867586</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.785419438732788e-05</v>
+        <v>0.0001494120224379003</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.591967732878402e-05</v>
+        <v>0.001214196323417127</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.577647582162172e-07</v>
+        <v>0.0001321572053711861</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0001331228268099949</v>
+        <v>0.001372413476929069</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.702542593004182e-05</v>
+        <v>0.001000705757178366</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.083460175432265e-05</v>
+        <v>0.0003293911868240684</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.520752453478053e-05</v>
+        <v>0.001609059050679207</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.532692112959921e-05</v>
+        <v>0.0007541885133832693</v>
       </c>
       <c r="BL4" t="n">
-        <v>3.547689630067907e-05</v>
+        <v>0.0001055121974786744</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.410120578133501e-05</v>
+        <v>0.0006553986459039152</v>
       </c>
       <c r="BN4" t="n">
-        <v>8.811171937850304e-06</v>
+        <v>0.0003248807333875448</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.885004404466599e-05</v>
+        <v>0.0006561685586348176</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.568694642628543e-05</v>
+        <v>0.0009670793078839779</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.065468136919662e-06</v>
+        <v>0.0004305509210098535</v>
       </c>
       <c r="BR4" t="n">
-        <v>4.415220246301033e-06</v>
+        <v>3.273828042438254e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.912274638016243e-05</v>
+        <v>0.000277714803814888</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.155038136057556e-06</v>
+        <v>0.0001768856163835153</v>
       </c>
       <c r="BU4" t="n">
-        <v>2.386566120549105e-05</v>
+        <v>5.686264194082469e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0001811315305531025</v>
+        <v>0.002350888215005398</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.304804573010188e-05</v>
+        <v>0.0002245411451440305</v>
       </c>
       <c r="BX4" t="n">
-        <v>3.286975334049203e-05</v>
+        <v>0.00160276354290545</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.75078145932639e-05</v>
+        <v>0.0007486902759410441</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0001259109412785619</v>
+        <v>0.0009155627922154963</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.503857467672788e-05</v>
+        <v>0.001090395264327526</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.34246199397603e-05</v>
+        <v>0.0002635704004205763</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.893303280870896e-05</v>
+        <v>0.0007021615747362375</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.325854049762711e-05</v>
+        <v>0.0001795429998310283</v>
       </c>
       <c r="CE4" t="n">
-        <v>8.838780195219442e-05</v>
+        <v>0.002083900850266218</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.965546991617884e-05</v>
+        <v>0.0002980533754453063</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.604140900075436e-05</v>
+        <v>0.001694883219897747</v>
       </c>
       <c r="CH4" t="n">
-        <v>3.187026959494688e-05</v>
+        <v>0.0002587874187156558</v>
       </c>
       <c r="CI4" t="n">
-        <v>4.615637226379476e-05</v>
+        <v>9.130527178058401e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.35219831665745e-05</v>
+        <v>6.895022670505568e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>4.406351763464045e-06</v>
+        <v>4.805398566531949e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>3.125894363620318e-05</v>
+        <v>0.0002477675443515182</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.335439421585761e-05</v>
+        <v>0.0002970532514154911</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.046497618517606e-05</v>
+        <v>0.00197779037989676</v>
       </c>
       <c r="CO4" t="n">
-        <v>4.250279380357824e-05</v>
+        <v>0.001349923899397254</v>
       </c>
       <c r="CP4" t="n">
-        <v>6.979965110076591e-05</v>
+        <v>0.001854775007814169</v>
       </c>
       <c r="CQ4" t="n">
-        <v>8.506204176228493e-05</v>
+        <v>0.0001084334508050233</v>
       </c>
       <c r="CR4" t="n">
-        <v>5.92457436141558e-05</v>
+        <v>0.0004089450521860272</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.386628329986706e-05</v>
+        <v>0.0005523642175830901</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.000105247920146212</v>
+        <v>0.0009469775250181556</v>
       </c>
       <c r="CU4" t="n">
-        <v>7.666432793485001e-06</v>
+        <v>0.000433448061812669</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.539606066420674e-05</v>
+        <v>0.000261768203927204</v>
       </c>
       <c r="CW4" t="n">
-        <v>6.867467163829133e-05</v>
+        <v>0.002202266361564398</v>
       </c>
       <c r="CX4" t="n">
-        <v>3.044667573703919e-05</v>
+        <v>0.0003119979228358716</v>
       </c>
       <c r="CY4" t="n">
-        <v>6.147228123154491e-05</v>
+        <v>0.00184734771028161</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.009473221027292e-05</v>
+        <v>0.0004785551282111555</v>
       </c>
       <c r="DA4" t="n">
-        <v>5.913524000789039e-05</v>
+        <v>0.000173853593878448</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.668181721470319e-05</v>
+        <v>1.148286173702218e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>5.537658580578864e-07</v>
+        <v>3.28255227941554e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.124303500750102e-05</v>
+        <v>0.0003787726745940745</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.448288250889163e-05</v>
+        <v>0.001252065761946142</v>
       </c>
       <c r="DF4" t="n">
-        <v>9.2616472102236e-05</v>
+        <v>0.001357585191726685</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.117947886086768e-05</v>
+        <v>0.0006483713514171541</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0001359528978355229</v>
+        <v>0.001522598089650273</v>
       </c>
       <c r="DI4" t="n">
-        <v>3.22217820212245e-05</v>
+        <v>0.00118331192061305</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.640373739064671e-05</v>
+        <v>0.001703318674117327</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.599985550157726e-05</v>
+        <v>0.0007428316166624427</v>
       </c>
       <c r="DL4" t="n">
-        <v>5.951410275883973e-05</v>
+        <v>0.001573146088048816</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.324852200923488e-05</v>
+        <v>6.940375169506297e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>6.17939222138375e-05</v>
+        <v>0.000209848236409016</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.323192711628508e-05</v>
+        <v>0.00123644364066422</v>
       </c>
       <c r="DP4" t="n">
-        <v>2.065095213765744e-05</v>
+        <v>0.0001881229545688257</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.064754178514704e-05</v>
+        <v>0.001382427988573909</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.915614120662212e-06</v>
+        <v>0.0007720518624410033</v>
       </c>
       <c r="DS4" t="n">
-        <v>7.623288547620177e-05</v>
+        <v>0.0004581077955663204</v>
       </c>
       <c r="DT4" t="n">
-        <v>1.047326804837212e-05</v>
+        <v>0.001498710596933961</v>
       </c>
       <c r="DU4" t="n">
-        <v>9.259123544325121e-06</v>
+        <v>0.0006819956470280886</v>
       </c>
       <c r="DV4" t="n">
-        <v>4.339355291449465e-05</v>
+        <v>0.001830621273256838</v>
       </c>
       <c r="DW4" t="n">
-        <v>4.264013477950357e-05</v>
+        <v>0.0001691993966232985</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.178225465992e-05</v>
+        <v>0.0006887221243232489</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.000106647152279038</v>
+        <v>3.473804099485278e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.65309245151002e-05</v>
+        <v>0.001127366092987359</v>
       </c>
       <c r="EA4" t="n">
-        <v>6.95234484737739e-05</v>
+        <v>0.0006019702996127307</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.456153768231161e-05</v>
+        <v>0.001430492382496595</v>
       </c>
       <c r="EC4" t="n">
-        <v>6.111875336500816e-06</v>
+        <v>0.0001398977183271199</v>
       </c>
       <c r="ED4" t="n">
-        <v>2.661170401552226e-05</v>
+        <v>0.003122076159343123</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.313881512032822e-05</v>
+        <v>0.001335225068032742</v>
       </c>
       <c r="EF4" t="n">
-        <v>2.052084346360061e-05</v>
+        <v>0.0006045509362593293</v>
       </c>
       <c r="EG4" t="n">
-        <v>3.828223270829767e-05</v>
+        <v>0.0012808971805498</v>
       </c>
       <c r="EH4" t="n">
-        <v>7.85005704528885e-06</v>
+        <v>0.0003927240322809666</v>
       </c>
       <c r="EI4" t="n">
-        <v>3.204232780262828e-05</v>
+        <v>0.00156000442802906</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1.137581193688675e-06</v>
+        <v>0.0007013474823907018</v>
       </c>
       <c r="EK4" t="n">
-        <v>4.251194332027808e-05</v>
+        <v>5.070193583378568e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>2.501751805539243e-05</v>
+        <v>0.0002737592440098524</v>
       </c>
       <c r="EM4" t="n">
-        <v>2.904127541114576e-05</v>
+        <v>8.942434942582622e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>5.282397069095168e-06</v>
+        <v>0.0001252734509762377</v>
       </c>
       <c r="EO4" t="n">
-        <v>2.78600309684407e-05</v>
+        <v>2.522969589335844e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>7.156277570175007e-05</v>
+        <v>0.001867636339738965</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.431616510672029e-05</v>
+        <v>1.966088893823326e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>4.973063551005907e-05</v>
+        <v>0.000377109827240929</v>
       </c>
       <c r="ES4" t="n">
-        <v>6.202334770932794e-05</v>
+        <v>0.0004572128527797759</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0001690502103883773</v>
+        <v>0.0006749742897227407</v>
       </c>
       <c r="EU4" t="n">
-        <v>8.053588317125104e-06</v>
+        <v>0.0006975696887820959</v>
       </c>
       <c r="EV4" t="n">
-        <v>2.128617052221671e-05</v>
+        <v>0.0002009492891374975</v>
       </c>
       <c r="EW4" t="n">
-        <v>2.432280234643258e-05</v>
+        <v>0.001026430982165039</v>
       </c>
       <c r="EX4" t="n">
-        <v>2.3039410734782e-05</v>
+        <v>8.149347559083253e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>7.635373913217336e-05</v>
+        <v>0.002245053881779313</v>
       </c>
       <c r="EZ4" t="n">
-        <v>7.358808943536133e-06</v>
+        <v>0.0001612722408026457</v>
       </c>
       <c r="FA4" t="n">
-        <v>4.241320857545361e-05</v>
+        <v>0.00186729640699923</v>
       </c>
       <c r="FB4" t="n">
-        <v>2.983811100421008e-05</v>
+        <v>0.0003497096186038107</v>
       </c>
       <c r="FC4" t="n">
-        <v>5.405360570875928e-05</v>
+        <v>0.0002004734269576147</v>
       </c>
       <c r="FD4" t="n">
-        <v>1.975129089260008e-05</v>
+        <v>9.882111044134945e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>6.454363756347448e-06</v>
+        <v>0.0003201670479029417</v>
       </c>
       <c r="FF4" t="n">
-        <v>2.6449873985257e-05</v>
+        <v>0.0004328061477281153</v>
       </c>
       <c r="FG4" t="n">
-        <v>4.89801459480077e-06</v>
+        <v>0.0001481857470935211</v>
       </c>
       <c r="FH4" t="n">
-        <v>2.88332266791258e-05</v>
+        <v>0.0006934241391718388</v>
       </c>
       <c r="FI4" t="n">
-        <v>2.031691656156909e-05</v>
+        <v>0.0007758619613014162</v>
       </c>
       <c r="FJ4" t="n">
-        <v>7.785631169099361e-05</v>
+        <v>0.0004551016609184444</v>
       </c>
       <c r="FK4" t="n">
-        <v>1.243665610672906e-05</v>
+        <v>0.0001901376526802778</v>
       </c>
       <c r="FL4" t="n">
-        <v>1.713247365842108e-05</v>
+        <v>0.0006109236273914576</v>
       </c>
       <c r="FM4" t="n">
-        <v>3.443710374995135e-05</v>
+        <v>0.000414011359680444</v>
       </c>
       <c r="FN4" t="n">
-        <v>1.89268212125171e-05</v>
+        <v>0.001467854133807123</v>
       </c>
       <c r="FO4" t="n">
-        <v>7.24377459846437e-05</v>
+        <v>0.0008461419492959976</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.98963936479413e-06</v>
+        <v>0.000562812143471092</v>
       </c>
       <c r="FQ4" t="n">
-        <v>2.005523310799617e-05</v>
+        <v>0.000683720107190311</v>
       </c>
       <c r="FR4" t="n">
-        <v>4.169794556219131e-05</v>
+        <v>0.0002456871443428099</v>
       </c>
       <c r="FS4" t="n">
-        <v>8.320096821989864e-05</v>
+        <v>0.001961038913577795</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001657266984693706</v>
+        <v>0.0008603341411799192</v>
       </c>
       <c r="FU4" t="n">
-        <v>1.565150159876794e-05</v>
+        <v>0.001290249871090055</v>
       </c>
       <c r="FV4" t="n">
-        <v>1.528265420347452e-05</v>
+        <v>0.0002035958896158263</v>
       </c>
       <c r="FW4" t="n">
-        <v>4.492583320825361e-05</v>
+        <v>8.864128903951496e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>3.670001024147496e-05</v>
+        <v>0.002129760570824146</v>
       </c>
       <c r="FY4" t="n">
-        <v>3.542516424204223e-05</v>
+        <v>0.0003746025904547423</v>
       </c>
       <c r="FZ4" t="n">
-        <v>3.525693682604469e-05</v>
+        <v>0.001085232943296432</v>
       </c>
       <c r="GA4" t="n">
-        <v>2.740717536653392e-05</v>
+        <v>0.0002832818427123129</v>
       </c>
       <c r="GB4" t="n">
-        <v>2.190566192439292e-05</v>
+        <v>0.001589653780683875</v>
       </c>
       <c r="GC4" t="n">
-        <v>9.141337795881554e-05</v>
+        <v>0.002044272609055042</v>
       </c>
       <c r="GD4" t="n">
-        <v>4.686623651650734e-05</v>
+        <v>0.0005276459269225597</v>
       </c>
       <c r="GE4" t="n">
-        <v>8.899412205209956e-05</v>
+        <v>0.001932139275595546</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.840793811425101e-05</v>
+        <v>0.0003565502702258527</v>
       </c>
       <c r="GG4" t="n">
-        <v>3.783975262194872e-05</v>
+        <v>0.0001761357998475432</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3.993773134425282e-07</v>
+        <v>0.00122419442050159</v>
       </c>
       <c r="B5" t="n">
-        <v>7.331662345677614e-05</v>
+        <v>0.00272032618522644</v>
       </c>
       <c r="C5" t="n">
-        <v>1.38811528813676e-05</v>
+        <v>0.0005514585063792765</v>
       </c>
       <c r="D5" t="n">
-        <v>2.506949022063054e-05</v>
+        <v>0.0002222481416538358</v>
       </c>
       <c r="E5" t="n">
-        <v>1.270223947358318e-05</v>
+        <v>0.0003878385468851775</v>
       </c>
       <c r="F5" t="n">
-        <v>4.820540925720707e-05</v>
+        <v>0.003642325755208731</v>
       </c>
       <c r="G5" t="n">
-        <v>7.59316208132077e-07</v>
+        <v>0.0007215514779090881</v>
       </c>
       <c r="H5" t="n">
-        <v>7.668593752896413e-06</v>
+        <v>0.0009616452152840793</v>
       </c>
       <c r="I5" t="n">
-        <v>8.059645551838912e-06</v>
+        <v>0.0007046996615827084</v>
       </c>
       <c r="J5" t="n">
-        <v>3.324302269902546e-06</v>
+        <v>0.001029039965942502</v>
       </c>
       <c r="K5" t="n">
-        <v>6.459909491240978e-05</v>
+        <v>0.00346177164465189</v>
       </c>
       <c r="L5" t="n">
-        <v>5.314631380315404e-06</v>
+        <v>0.0008061526459641755</v>
       </c>
       <c r="M5" t="n">
-        <v>3.40717779181432e-05</v>
+        <v>0.0004587821022141725</v>
       </c>
       <c r="N5" t="n">
-        <v>3.446592745603994e-05</v>
+        <v>0.0009746697032824159</v>
       </c>
       <c r="O5" t="n">
-        <v>5.869064625585452e-05</v>
+        <v>0.003658670466393232</v>
       </c>
       <c r="P5" t="n">
-        <v>1.815001087379642e-05</v>
+        <v>7.709108467679471e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.246038573299302e-05</v>
+        <v>0.0001251601788681</v>
       </c>
       <c r="R5" t="n">
-        <v>6.874195150885498e-06</v>
+        <v>0.001195543445646763</v>
       </c>
       <c r="S5" t="n">
-        <v>4.164353413216304e-06</v>
+        <v>0.0001298463903367519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.464317938371096e-05</v>
+        <v>0.0003808704495895654</v>
       </c>
       <c r="U5" t="n">
-        <v>2.988943606396788e-06</v>
+        <v>0.000650103553198278</v>
       </c>
       <c r="V5" t="n">
-        <v>8.295196494145785e-07</v>
+        <v>0.001166120637208223</v>
       </c>
       <c r="W5" t="n">
-        <v>3.047573954972904e-06</v>
+        <v>0.0006872409139759839</v>
       </c>
       <c r="X5" t="n">
-        <v>1.20593231258681e-05</v>
+        <v>0.0002523850416764617</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.886269829919911e-07</v>
+        <v>0.0001481713552493602</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.787348987316363e-06</v>
+        <v>0.0004532373568508774</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.701223694311921e-07</v>
+        <v>0.0002786516561172903</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.279966454603709e-05</v>
+        <v>4.363332118373364e-05</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.692769546934869e-05</v>
+        <v>0.0007857232121750712</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78516456799116e-05</v>
+        <v>0.0001298333372687921</v>
       </c>
       <c r="AE5" t="n">
-        <v>9.693217180029023e-06</v>
+        <v>0.00149773876182735</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.057215715467464e-05</v>
+        <v>0.0009306850843131542</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.076111129805213e-05</v>
+        <v>0.0006632325821556151</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.395883373334073e-05</v>
+        <v>0.000223066279431805</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.222908501105849e-06</v>
+        <v>0.001904149656184018</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11038002614805e-06</v>
+        <v>0.0002409935113973916</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.356717343194759e-06</v>
+        <v>0.000159840565174818</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.366520427836804e-05</v>
+        <v>0.0006010914221405983</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.772328346305585e-06</v>
+        <v>0.0006261883536353707</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.374588191538351e-05</v>
+        <v>0.0008916587103158236</v>
       </c>
       <c r="AO5" t="n">
-        <v>9.949950481313863e-07</v>
+        <v>0.0002246569201815873</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.112537574954331e-05</v>
+        <v>0.0004914850578643382</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.128572057496058e-05</v>
+        <v>0.0002911764895543456</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.890873009979259e-06</v>
+        <v>0.0009939635638147593</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.453172207126045e-07</v>
+        <v>0.0005642426549457014</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.08987815110595e-05</v>
+        <v>0.0006528542144224048</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.343435623217374e-05</v>
+        <v>0.003209535731002688</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.234511940623634e-07</v>
+        <v>0.0006499584414996207</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.021215848595602e-05</v>
+        <v>0.0003447403432801366</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.267545823997352e-05</v>
+        <v>0.0007080389186739922</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.596400215930771e-05</v>
+        <v>0.002145900158211589</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.091000169457402e-05</v>
+        <v>0.0003259064396843314</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.204146070056595e-06</v>
+        <v>3.039171861018986e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.307018465013243e-05</v>
+        <v>0.0003514163545332849</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.137238425348187e-06</v>
+        <v>0.0001110089215217158</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.010935168073047e-05</v>
+        <v>0.0002137082919944078</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.513172810518881e-05</v>
+        <v>0.0005259255412966013</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.001603868644452e-05</v>
+        <v>2.438438241370022e-05</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.812965198652819e-05</v>
+        <v>0.0003296267823316157</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.456734339124523e-05</v>
+        <v>0.0007653708453290164</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.789305497368332e-05</v>
+        <v>0.0001579031813889742</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.154984420281835e-05</v>
+        <v>0.0006160789635032415</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.332729647809174e-07</v>
+        <v>0.0006864623865112662</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.068960318661993e-05</v>
+        <v>6.919066800037399e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.663325633671775e-06</v>
+        <v>0.0008448249427601695</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.933027856983244e-06</v>
+        <v>2.809557554428466e-05</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.134404212483787e-06</v>
+        <v>0.0001041337527567521</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.25427356781438e-06</v>
+        <v>0.0006788632017560303</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.882914698915556e-06</v>
+        <v>0.0008478971431031823</v>
       </c>
       <c r="BR5" t="n">
-        <v>1.3022919119976e-05</v>
+        <v>0.001389161800034344</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.493900061992463e-06</v>
+        <v>2.682816193555482e-05</v>
       </c>
       <c r="BT5" t="n">
-        <v>2.286492644998361e-06</v>
+        <v>0.001003652112558484</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.693550181400497e-06</v>
+        <v>3.162591019645333e-05</v>
       </c>
       <c r="BV5" t="n">
-        <v>2.579143074399326e-05</v>
+        <v>0.002029230818152428</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.580939149600454e-06</v>
+        <v>0.0004729614011012018</v>
       </c>
       <c r="BX5" t="n">
-        <v>4.81568986288039e-06</v>
+        <v>0.001103461720049381</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.311150850204285e-06</v>
+        <v>0.0001140370732173324</v>
       </c>
       <c r="BZ5" t="n">
-        <v>9.522346772428136e-06</v>
+        <v>0.001381913083605468</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.567025477328571e-06</v>
+        <v>0.0004540699883364141</v>
       </c>
       <c r="CB5" t="n">
-        <v>9.627808594814269e-07</v>
+        <v>0.0001385771174682304</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.323660050431499e-06</v>
+        <v>0.0004246792523190379</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.471087428712053e-07</v>
+        <v>0.0005206589703448117</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.331569364992902e-05</v>
+        <v>0.0008733185823075473</v>
       </c>
       <c r="CF5" t="n">
-        <v>7.655128797523503e-07</v>
+        <v>7.466097304131836e-05</v>
       </c>
       <c r="CG5" t="n">
-        <v>1.515823555564566e-06</v>
+        <v>0.0006471093511208892</v>
       </c>
       <c r="CH5" t="n">
-        <v>3.602355036491645e-06</v>
+        <v>0.0003813796502072364</v>
       </c>
       <c r="CI5" t="n">
-        <v>6.67122139930143e-06</v>
+        <v>0.0009369070176035166</v>
       </c>
       <c r="CJ5" t="n">
-        <v>9.055485861608759e-06</v>
+        <v>0.0004122611717320979</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.760129407557542e-06</v>
+        <v>0.000296801415970549</v>
       </c>
       <c r="CL5" t="n">
-        <v>3.011115950357635e-06</v>
+        <v>0.0002056320081464946</v>
       </c>
       <c r="CM5" t="n">
-        <v>7.795867531967815e-06</v>
+        <v>9.479426080361009e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.140870062954491e-05</v>
+        <v>0.001577395829372108</v>
       </c>
       <c r="CO5" t="n">
-        <v>2.038779257418355e-06</v>
+        <v>0.0005681709735654294</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.038474329106975e-05</v>
+        <v>0.000119274714961648</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.107164729954093e-07</v>
+        <v>7.800053572282195e-05</v>
       </c>
       <c r="CR5" t="n">
-        <v>8.741058081795927e-07</v>
+        <v>0.0004145489074289799</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.351948594674468e-05</v>
+        <v>0.0008674178970977664</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.223520641564392e-05</v>
+        <v>0.0002353994059376419</v>
       </c>
       <c r="CU5" t="n">
-        <v>9.472541023569647e-06</v>
+        <v>0.0003470521769486368</v>
       </c>
       <c r="CV5" t="n">
-        <v>9.61434807322803e-07</v>
+        <v>0.0003489481168799102</v>
       </c>
       <c r="CW5" t="n">
-        <v>9.393335858476348e-06</v>
+        <v>0.0007745680632069707</v>
       </c>
       <c r="CX5" t="n">
-        <v>3.930697857867926e-06</v>
+        <v>2.980984572786838e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.480119519532309e-06</v>
+        <v>0.0005587419727817178</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.9964238567336e-06</v>
+        <v>0.0003110933175776154</v>
       </c>
       <c r="DA5" t="n">
-        <v>7.46059004086419e-06</v>
+        <v>0.0008980593411251903</v>
       </c>
       <c r="DB5" t="n">
-        <v>5.696721927961335e-06</v>
+        <v>0.0002121865400113165</v>
       </c>
       <c r="DC5" t="n">
-        <v>3.965046744269785e-07</v>
+        <v>0.0002914808283094317</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.351068815187318e-06</v>
+        <v>0.0001823947095545009</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.046109628077829e-05</v>
+        <v>4.37793496530503e-05</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.692060141067486e-05</v>
+        <v>0.0006282319081947207</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.034714452747721e-05</v>
+        <v>0.0003561636549420655</v>
       </c>
       <c r="DH5" t="n">
-        <v>2.754724846454337e-06</v>
+        <v>0.0006043730536475778</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.764974149409682e-05</v>
+        <v>0.0006522809853777289</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.771314939309377e-05</v>
+        <v>0.0007841135375201702</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.350916318187956e-05</v>
+        <v>9.378389222547412e-06</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.609710670891218e-05</v>
+        <v>0.0008241698378697038</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.3181510186987e-06</v>
+        <v>0.0006069183582440019</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.463047055949573e-06</v>
+        <v>8.722901111468673e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>7.719929271843284e-06</v>
+        <v>0.0005156625993549824</v>
       </c>
       <c r="DP5" t="n">
-        <v>1.049506522576849e-06</v>
+        <v>0.0003149837139062583</v>
       </c>
       <c r="DQ5" t="n">
-        <v>2.398166907369159e-05</v>
+        <v>0.0008967539761215448</v>
       </c>
       <c r="DR5" t="n">
-        <v>1.086880729417317e-05</v>
+        <v>0.0001893127773655578</v>
       </c>
       <c r="DS5" t="n">
-        <v>1.512024755356833e-05</v>
+        <v>0.0005759320338256657</v>
       </c>
       <c r="DT5" t="n">
-        <v>3.38123618348618e-06</v>
+        <v>7.305345934582874e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>5.522604169527767e-06</v>
+        <v>0.0002846670395229012</v>
       </c>
       <c r="DV5" t="n">
-        <v>1.923480112964171e-06</v>
+        <v>0.0002160142175853252</v>
       </c>
       <c r="DW5" t="n">
-        <v>5.88319653616054e-06</v>
+        <v>0.0003803962026722729</v>
       </c>
       <c r="DX5" t="n">
-        <v>3.30544708049274e-06</v>
+        <v>8.670391252962872e-05</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.129695414827438e-06</v>
+        <v>0.0001976179773919284</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.074432632070966e-05</v>
+        <v>0.0002446369617246091</v>
       </c>
       <c r="EA5" t="n">
-        <v>7.384244327113265e-09</v>
+        <v>0.0003525141219142824</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.684048584138509e-05</v>
+        <v>0.001063078409060836</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.416005761711858e-05</v>
+        <v>0.0003656827029772103</v>
       </c>
       <c r="ED5" t="n">
-        <v>2.565982686064672e-05</v>
+        <v>0.000418515526689589</v>
       </c>
       <c r="EE5" t="n">
-        <v>5.696551397704752e-06</v>
+        <v>0.0008981337305158377</v>
       </c>
       <c r="EF5" t="n">
-        <v>4.052662461617729e-06</v>
+        <v>0.0005132185760885477</v>
       </c>
       <c r="EG5" t="n">
-        <v>9.503713044978213e-06</v>
+        <v>8.846132550388575e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>2.186417532357154e-06</v>
+        <v>0.0003378958208486438</v>
       </c>
       <c r="EI5" t="n">
-        <v>2.085435153276194e-05</v>
+        <v>0.000625628512352705</v>
       </c>
       <c r="EJ5" t="n">
-        <v>8.851254278852139e-06</v>
+        <v>0.0006981109036132693</v>
       </c>
       <c r="EK5" t="n">
-        <v>1.754502591211349e-06</v>
+        <v>0.0003075531567446887</v>
       </c>
       <c r="EL5" t="n">
-        <v>1.870312553364784e-05</v>
+        <v>4.435948358150199e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>7.392459338007029e-07</v>
+        <v>1.026120844471734e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.172273982774641e-06</v>
+        <v>0.0002851088938768953</v>
       </c>
       <c r="EO5" t="n">
-        <v>2.075795009659487e-06</v>
+        <v>0.0003388618933968246</v>
       </c>
       <c r="EP5" t="n">
-        <v>3.460165544311167e-06</v>
+        <v>0.0003492636897135526</v>
       </c>
       <c r="EQ5" t="n">
-        <v>8.115648597595282e-06</v>
+        <v>4.412277485243976e-05</v>
       </c>
       <c r="ER5" t="n">
-        <v>9.494740879745223e-06</v>
+        <v>0.0007431709673255682</v>
       </c>
       <c r="ES5" t="n">
-        <v>1.317980149906361e-05</v>
+        <v>0.0009161378256976604</v>
       </c>
       <c r="ET5" t="n">
-        <v>2.373522147536278e-05</v>
+        <v>0.000715138332452625</v>
       </c>
       <c r="EU5" t="n">
-        <v>3.018723418790614e-06</v>
+        <v>0.0003236872144043446</v>
       </c>
       <c r="EV5" t="n">
-        <v>2.743301138252718e-06</v>
+        <v>0.0003340308321639895</v>
       </c>
       <c r="EW5" t="n">
-        <v>6.495813522633398e-07</v>
+        <v>0.0003101326292380691</v>
       </c>
       <c r="EX5" t="n">
-        <v>5.619726834993344e-07</v>
+        <v>0.0004770687373820692</v>
       </c>
       <c r="EY5" t="n">
-        <v>9.939787560142577e-06</v>
+        <v>0.0009871753863990307</v>
       </c>
       <c r="EZ5" t="n">
-        <v>7.159293318181881e-07</v>
+        <v>5.876790964975953e-08</v>
       </c>
       <c r="FA5" t="n">
-        <v>1.377777607558528e-06</v>
+        <v>0.0005143028683960438</v>
       </c>
       <c r="FB5" t="n">
-        <v>5.940750270383433e-06</v>
+        <v>0.0005197287537157536</v>
       </c>
       <c r="FC5" t="n">
-        <v>8.068333045230247e-06</v>
+        <v>0.0007966228295117617</v>
       </c>
       <c r="FD5" t="n">
-        <v>6.27239205641672e-06</v>
+        <v>0.0003328449965920299</v>
       </c>
       <c r="FE5" t="n">
-        <v>2.231691269116709e-06</v>
+        <v>0.0002585355250630528</v>
       </c>
       <c r="FF5" t="n">
-        <v>2.154274170607096e-06</v>
+        <v>0.0001028120750561357</v>
       </c>
       <c r="FG5" t="n">
-        <v>8.247859568655258e-07</v>
+        <v>0.0001303760218434036</v>
       </c>
       <c r="FH5" t="n">
-        <v>2.466972091497155e-06</v>
+        <v>0.00106504769064486</v>
       </c>
       <c r="FI5" t="n">
-        <v>2.363735120525234e-06</v>
+        <v>0.0003956126747652888</v>
       </c>
       <c r="FJ5" t="n">
-        <v>1.926616278069559e-05</v>
+        <v>0.0004345892812125385</v>
       </c>
       <c r="FK5" t="n">
-        <v>1.962078385986388e-05</v>
+        <v>0.0002598207211121917</v>
       </c>
       <c r="FL5" t="n">
-        <v>6.143775408418151e-06</v>
+        <v>0.00115469703450799</v>
       </c>
       <c r="FM5" t="n">
-        <v>8.777979019214399e-06</v>
+        <v>0.0006233442691154778</v>
       </c>
       <c r="FN5" t="n">
-        <v>2.379526449658442e-05</v>
+        <v>0.001253930735401809</v>
       </c>
       <c r="FO5" t="n">
-        <v>7.388741323666181e-06</v>
+        <v>0.0005796217010356486</v>
       </c>
       <c r="FP5" t="n">
-        <v>8.262277333415113e-06</v>
+        <v>7.765959890093654e-05</v>
       </c>
       <c r="FQ5" t="n">
-        <v>2.585355468909256e-05</v>
+        <v>0.0007197883678600192</v>
       </c>
       <c r="FR5" t="n">
-        <v>1.257940130017232e-05</v>
+        <v>0.001118212705478072</v>
       </c>
       <c r="FS5" t="n">
-        <v>2.119620694429614e-05</v>
+        <v>0.0002280667686136439</v>
       </c>
       <c r="FT5" t="n">
-        <v>2.035107536357827e-05</v>
+        <v>0.0002540845889598131</v>
       </c>
       <c r="FU5" t="n">
-        <v>2.502725874364842e-05</v>
+        <v>0.0002936758100986481</v>
       </c>
       <c r="FV5" t="n">
-        <v>2.266864248667844e-05</v>
+        <v>1.595237699802965e-05</v>
       </c>
       <c r="FW5" t="n">
-        <v>5.336974481906509e-06</v>
+        <v>0.000954223214648664</v>
       </c>
       <c r="FX5" t="n">
-        <v>1.282037464989116e-05</v>
+        <v>0.0009331487817689776</v>
       </c>
       <c r="FY5" t="n">
-        <v>5.298093583405716e-06</v>
+        <v>0.0005865602870471776</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.130208420363488e-05</v>
+        <v>0.0002331955474801362</v>
       </c>
       <c r="GA5" t="n">
-        <v>2.063237116090022e-05</v>
+        <v>0.000491672137286514</v>
       </c>
       <c r="GB5" t="n">
-        <v>3.834848030237481e-07</v>
+        <v>0.0006721234531141818</v>
       </c>
       <c r="GC5" t="n">
-        <v>2.818336497512064e-06</v>
+        <v>0.001300521311350167</v>
       </c>
       <c r="GD5" t="n">
-        <v>6.090435363148572e-06</v>
+        <v>0.0009593233116902411</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.480648618075065e-06</v>
+        <v>6.930579547770321e-05</v>
       </c>
       <c r="GF5" t="n">
-        <v>5.516479177458677e-06</v>
+        <v>6.461469456553459e-05</v>
       </c>
       <c r="GG5" t="n">
-        <v>1.030314615491079e-05</v>
+        <v>0.0007545360713265836</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.008337026461958885</v>
+        <v>0.000112190842628479</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04195511713624001</v>
+        <v>0.01262437552213669</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002908228663727641</v>
+        <v>0.003201390616595745</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01748409122228622</v>
+        <v>0.01033161394298077</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005987092852592468</v>
+        <v>0.001051655737683177</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009918354451656342</v>
+        <v>0.008653619326651096</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001969195436686277</v>
+        <v>0.00511523149907589</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00311191868968308</v>
+        <v>0.00602979538962245</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007141405949369073</v>
+        <v>0.0004139735538046807</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0101968077942729</v>
+        <v>0.0003483783802948892</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02542578428983688</v>
+        <v>0.0127413310110569</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001849665772169828</v>
+        <v>0.005503440741449594</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01669742725789547</v>
+        <v>0.01460179779678583</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01266420632600784</v>
+        <v>0.004033863078802824</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01469221524894238</v>
+        <v>0.007668752688914537</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001169866882264614</v>
+        <v>0.006233291700482368</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001354412292130291</v>
+        <v>0.003046782687306404</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003525836393237114</v>
+        <v>0.0009249948197975755</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004409290268085897</v>
+        <v>2.306887472514063e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003960245288908482</v>
+        <v>0.0002303413057234138</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0009175762534141541</v>
+        <v>0.0001329368096776307</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00635362695902586</v>
+        <v>0.0003393336373846978</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005703432019799948</v>
+        <v>0.001140061416663229</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002733406610786915</v>
+        <v>0.003331029089167714</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.004095453303307295</v>
+        <v>0.0008939097751863301</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002539664739742875</v>
+        <v>0.001990544609725475</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003093914361670613</v>
+        <v>0.002228266792371869</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001172003801912069</v>
+        <v>0.0004257234686519951</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.007001605350524187</v>
+        <v>0.001922462834045291</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0008324551745317876</v>
+        <v>0.001644482719711959</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002629113616421819</v>
+        <v>0.001740190433338284</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004253712948411703</v>
+        <v>0.0003371895290911198</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.001632692408747971</v>
+        <v>0.005560266319662333</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0002554217353463173</v>
+        <v>0.0009071066742762923</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0007786264177411795</v>
+        <v>0.002763900673016906</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001279835822060704</v>
+        <v>0.0008768661646172404</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.002681891899555922</v>
+        <v>0.0003770960902329534</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.004342000465840101</v>
+        <v>0.003678401466459036</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0001897157490020618</v>
+        <v>0.002982041798532009</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001449968898668885</v>
+        <v>0.002422135323286057</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003385679330676794</v>
+        <v>0.001621811301447451</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.006219206843525171</v>
+        <v>0.003097050590440631</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.363110151141882e-05</v>
+        <v>0.001302488148212433</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0004968221765011549</v>
+        <v>0.0003127920208498836</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.002430340275168419</v>
+        <v>0.0003395287785679102</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0006407788023352623</v>
+        <v>8.713756687939167e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.02849677391350269</v>
+        <v>0.006593259051442146</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0009781832341104746</v>
+        <v>0.002745399251580238</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.002842802321538329</v>
+        <v>0.005917861126363277</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.003286387072876096</v>
+        <v>0.009018827229738235</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001109118806198239</v>
+        <v>0.006256978027522564</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002116424264386296</v>
+        <v>0.0008127429755404592</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0007321385201066732</v>
+        <v>0.0002500181435607374</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002153741428628564</v>
+        <v>0.001687736483290792</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.003655500477179885</v>
+        <v>0.0007232909556478262</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.007366859819740057</v>
+        <v>0.0001024421217152849</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.004994453396648169</v>
+        <v>0.003303261008113623</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.002327155089005828</v>
+        <v>0.001237970660440624</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01078564208000898</v>
+        <v>0.004229360725730658</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006786015350371599</v>
+        <v>0.001449784962460399</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.003155500628054142</v>
+        <v>0.001344379736110568</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.003078626468777657</v>
+        <v>0.003854256123304367</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0002332373260287568</v>
+        <v>0.001538178534246981</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.003273608861491084</v>
+        <v>0.0004213927313685417</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.004965192172676325</v>
+        <v>0.0007784230401739478</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001197766978293657</v>
+        <v>0.000214810948818922</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.004107169806957245</v>
+        <v>0.001631958410143852</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.00353256007656455</v>
+        <v>0.001035400317050517</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.003240769961848855</v>
+        <v>0.0004324357723817229</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.003639145754277706</v>
+        <v>0.0004007482202723622</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.142973244190216e-06</v>
+        <v>0.001273867324925959</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.003521052654832602</v>
+        <v>0.0005312507273629308</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.001014054869301617</v>
+        <v>0.0003343018761370331</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01424819324165583</v>
+        <v>0.004169590771198273</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001954766688868403</v>
+        <v>0.001675658393651247</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.003801239421591163</v>
+        <v>0.004796008579432964</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.003711755620315671</v>
+        <v>0.001654052990488708</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.00676571112126112</v>
+        <v>0.004755668342113495</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0005901379627175629</v>
+        <v>0.001829817309044302</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.001462121726945043</v>
+        <v>0.000510570069309324</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.003204608336091042</v>
+        <v>0.001544933067634702</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.002602492924779654</v>
+        <v>0.0002038274687947705</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.006623005960136652</v>
+        <v>0.004358665551990271</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.002057523466646671</v>
+        <v>0.0006803612923249602</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.001747008645907044</v>
+        <v>0.003941808827221394</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001284678932279348</v>
+        <v>6.227717676665634e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.002546904608607292</v>
+        <v>0.001556686125695705</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001457932638004422</v>
+        <v>0.000205953125259839</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0005373912281356752</v>
+        <v>0.0009690564475022256</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.001416896586306393</v>
+        <v>0.0001785207714419812</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.002655861666426063</v>
+        <v>0.0001297317794524133</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0005644685588777065</v>
+        <v>0.002516423352062702</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.00370717654004693</v>
+        <v>0.005877573043107986</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.005321491975337267</v>
+        <v>0.005975333508104086</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.002657521516084671</v>
+        <v>0.0006857792614027858</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.004416904877871275</v>
+        <v>0.001531887915916741</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.002985172905027866</v>
+        <v>0.0005504704313352704</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.004412222653627396</v>
+        <v>0.002155225025489926</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0009985881624743342</v>
+        <v>0.000327633140841499</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0022374854888767</v>
+        <v>0.0001813926501199603</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.005036502610892057</v>
+        <v>0.004255914594978094</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.002138996031135321</v>
+        <v>0.00110000092536211</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.003561146790161729</v>
+        <v>0.004289226606488228</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001351513434201479</v>
+        <v>0.001008995342999697</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.003071777755394578</v>
+        <v>0.001664506853558123</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001785413245670497</v>
+        <v>0.0005131110665388405</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0008156761759892106</v>
+        <v>0.0009203132358379662</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0008568877819925547</v>
+        <v>0.0002874135971069336</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.003925836645066738</v>
+        <v>0.0008771601133048534</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.004451735410839319</v>
+        <v>0.003172258613631129</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.001934888772666454</v>
+        <v>0.001189606264233589</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.009194253943860531</v>
+        <v>0.003336956724524498</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.005905090365558863</v>
+        <v>0.0006336324149742723</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.002685434883460402</v>
+        <v>0.007099220063537359</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.00183603388722986</v>
+        <v>0.0004475959576666355</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.001504456275142729</v>
+        <v>0.006542952265590429</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.001078932778909802</v>
+        <v>0.002167421393096447</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.005077037960290909</v>
+        <v>4.612485645338893e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001314969966188073</v>
+        <v>0.002526292810216546</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.00317502673715353</v>
+        <v>0.001064923824742436</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.001006952486932278</v>
+        <v>0.001624616561457515</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001109823700971901</v>
+        <v>0.0005657848087139428</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.005516369361430407</v>
+        <v>0.001120531582273543</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0002230510581284761</v>
+        <v>0.002431127475574613</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0003839951823465526</v>
+        <v>0.001829917542636395</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.002102497732266784</v>
+        <v>0.004663475323468447</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.001798226381652057</v>
+        <v>7.64929864089936e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0003977154847234488</v>
+        <v>0.0002007313014473766</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.005701211281120777</v>
+        <v>0.002946396358311176</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.001713453559204936</v>
+        <v>0.001898254151456058</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.005437529645860195</v>
+        <v>0.0005704986397176981</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.002312179189175367</v>
+        <v>0.003130575409159064</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004386771470308304</v>
+        <v>0.0001534052717033774</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.001168480957858264</v>
+        <v>0.007073886692523956</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.001904727076180279</v>
+        <v>0.006161411758512259</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001870058476924896</v>
+        <v>0.001822861609980464</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.003355365712195635</v>
+        <v>0.002802935894578695</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0001409284450346604</v>
+        <v>0.002129582688212395</v>
       </c>
       <c r="EI7" t="n">
-        <v>3.400829154998064e-05</v>
+        <v>0.003891054540872574</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0009538430022075772</v>
+        <v>0.0009035008260980248</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.001822634367272258</v>
+        <v>0.00121313810814172</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.002122361212968826</v>
+        <v>6.367368041537702e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0009825348388403654</v>
+        <v>9.64081336860545e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001998773077502847</v>
+        <v>0.0003658491768874228</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.002746375044807792</v>
+        <v>0.0008125070598907769</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.005390276201069355</v>
+        <v>0.004300432279706001</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001477609970606863</v>
+        <v>0.0002889460884034634</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.004446793347597122</v>
+        <v>0.002619129372760653</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.004679327365010977</v>
+        <v>0.001003076555207372</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01108686998486519</v>
+        <v>0.0005053422646597028</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.00306465127505362</v>
+        <v>0.00183538522105664</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.004217176232486963</v>
+        <v>0.001112975063733757</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0007060314528644085</v>
+        <v>0.003016681410372257</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.001760215498507023</v>
+        <v>0.0001713001111056656</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.005461455322802067</v>
+        <v>0.004780426155775785</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0003864428435917944</v>
+        <v>0.000674079405143857</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.002765990793704987</v>
+        <v>0.004654758609831333</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0009146103984676301</v>
+        <v>0.0002548574702814221</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.003579800948500633</v>
+        <v>0.001689058030024171</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.002185341902077198</v>
+        <v>0.0006412304937839508</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.001136746839620173</v>
+        <v>0.001241502584889531</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.00176969263702631</v>
+        <v>0.0008377339108847082</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.001371523132547736</v>
+        <v>0.000294106372166425</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.002712148474529386</v>
+        <v>0.002031792188063264</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0008376361802220345</v>
+        <v>0.0003794535004999489</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.003823175095021725</v>
+        <v>0.002128700958564878</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.00148016307502985</v>
+        <v>0.001059870352037251</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.00231566745787859</v>
+        <v>7.198302773758769e-05</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0007877055904828012</v>
+        <v>0.001157709397375584</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.00245783943682909</v>
+        <v>0.000502241775393486</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.004324488807469606</v>
+        <v>0.001702760113403201</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.001918842550367117</v>
+        <v>0.002658983459696174</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.004833509679883718</v>
+        <v>0.005013755522668362</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001277289353311062</v>
+        <v>0.003496606834232807</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.003731852862983942</v>
+        <v>0.003749060910195112</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01114185154438019</v>
+        <v>0.004155242815613747</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.003393179271370173</v>
+        <v>0.001776321791112423</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0004788896767422557</v>
+        <v>0.001117793377488852</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0006825499003753066</v>
+        <v>0.004156870767474174</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.001968361204490066</v>
+        <v>0.003444936126470566</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.003815420903265476</v>
+        <v>0.001133560901507735</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.003358272835612297</v>
+        <v>0.0004773993277922273</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.001407673000358045</v>
+        <v>0.001887894351966679</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001625716802664101</v>
+        <v>0.003837863449007273</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.004929407499730587</v>
+        <v>0.0006948712980374694</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.004334128461778164</v>
+        <v>0.002659845165908337</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.008522408083081245</v>
+        <v>0.003383328672498465</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0002850256278179586</v>
+        <v>0.001050361432135105</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.001120923319831491</v>
+        <v>0.001091252663172781</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0005928369937464595</v>
+        <v>0.0001092152670025826</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002426889492198825</v>
+        <v>0.1197506934404373</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004222870920784771</v>
+        <v>0.008882930502295494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000706691644154489</v>
+        <v>0.02388284355401993</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001911196857690811</v>
+        <v>0.006862024776637554</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0005675768479704857</v>
+        <v>0.02916711196303368</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002005794522119686</v>
+        <v>0.03572604060173035</v>
       </c>
       <c r="H9" t="n">
-        <v>3.863043457386084e-05</v>
+        <v>0.03781819716095924</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001641650596866384</v>
+        <v>0.01635561510920525</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000126018567243591</v>
+        <v>0.02730333060026169</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001436837832443416</v>
+        <v>0.1204361468553543</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002662838087417185</v>
+        <v>0.009492063894867897</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0008169747306965292</v>
+        <v>0.06237486004829407</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001993207959458232</v>
+        <v>0.05277666077017784</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0007512776646763086</v>
+        <v>0.02656513080000877</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001725453766994178</v>
+        <v>0.009433434344828129</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0003128133248537779</v>
+        <v>0.02946503646671772</v>
       </c>
       <c r="R9" t="n">
-        <v>5.469885945785791e-05</v>
+        <v>0.0499129593372345</v>
       </c>
       <c r="S9" t="n">
-        <v>4.531181184574962e-05</v>
+        <v>0.01254626084119081</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0006311146426014602</v>
+        <v>0.05145162343978882</v>
       </c>
       <c r="U9" t="n">
-        <v>1.555506514705485e-07</v>
+        <v>0.005772322416305542</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0002270076947752386</v>
+        <v>0.02436027862131596</v>
       </c>
       <c r="W9" t="n">
-        <v>8.921424159780145e-05</v>
+        <v>0.01049115229398012</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0004048015689477324</v>
+        <v>0.01984349638223648</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002012817858485505</v>
+        <v>0.002383447950705886</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.54220668063499e-05</v>
+        <v>0.013673753477633</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.39203891903162e-05</v>
+        <v>0.004135806113481522</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.824708644766361e-05</v>
+        <v>0.008507322520017624</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.000528322474565357</v>
+        <v>0.0008552016224712133</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0003425660252105445</v>
+        <v>0.0052185975946486</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0003717084182426333</v>
+        <v>0.02460101991891861</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.2053491496481e-05</v>
+        <v>0.03341452404856682</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.321358210290782e-05</v>
+        <v>0.02303392998874187</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0005324189551174641</v>
+        <v>0.0009339991956949234</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0001437977334717289</v>
+        <v>0.04668024182319641</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0001024220400722697</v>
+        <v>0.007582924328744411</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0003569434629753232</v>
+        <v>0.011304278858006</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0005952176288701594</v>
+        <v>0.03102584928274155</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0001751185045577586</v>
+        <v>0.006694570183753967</v>
       </c>
       <c r="AN9" t="n">
-        <v>8.255569991888478e-05</v>
+        <v>0.02252328768372536</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0002353657182538882</v>
+        <v>0.008998474106192589</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0003457814455032349</v>
+        <v>0.0109582431614399</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001362803159281611</v>
+        <v>0.000200582027900964</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0001019876726786606</v>
+        <v>0.05333464220166206</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.851222810335457e-05</v>
+        <v>0.01194997783750296</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0003413396771065891</v>
+        <v>0.001693574711680412</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.002249531447887421</v>
+        <v>0.1257407516241074</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.625615737400949e-05</v>
+        <v>0.002167092636227608</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.971541395410895e-05</v>
+        <v>0.008302563801407814</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0001724819303490222</v>
+        <v>0.01677347347140312</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0004557110369205475</v>
+        <v>0.03424093872308731</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0001580195676069707</v>
+        <v>0.007064294070005417</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0001527471613371745</v>
+        <v>0.0195038877427578</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0001495105243520811</v>
+        <v>0.008795928210020065</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0001328131183981895</v>
+        <v>0.004559063352644444</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0002415414055576548</v>
+        <v>0.02102216705679893</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.551317397272214e-05</v>
+        <v>0.01920752972364426</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0003054765402339399</v>
+        <v>0.02198161371052265</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001281976932659745</v>
+        <v>0.04421704262495041</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0001662624854361638</v>
+        <v>0.004463046789169312</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0002902179548982531</v>
+        <v>0.02228951826691628</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0003277729556430131</v>
+        <v>0.005810388829559088</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0001823071215767413</v>
+        <v>0.01115477457642555</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0003754000645130873</v>
+        <v>0.000135310459882021</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.00058470678050071</v>
+        <v>0.00789747666567564</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.799433893116657e-07</v>
+        <v>0.01577932760119438</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0004960802034474909</v>
+        <v>0.01963412016630173</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.000627711764536798</v>
+        <v>0.01787529699504375</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0001830641849664971</v>
+        <v>0.01173835527151823</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0002092650975100696</v>
+        <v>0.02073502540588379</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.510275539360009e-05</v>
+        <v>0.005286508239805698</v>
       </c>
       <c r="BT9" t="n">
-        <v>3.031392407137901e-05</v>
+        <v>0.01156623288989067</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0001700671418802813</v>
+        <v>0.02312184683978558</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001091136829927564</v>
+        <v>0.1170605793595314</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0003835895622614771</v>
+        <v>0.0170537605881691</v>
       </c>
       <c r="BX9" t="n">
-        <v>2.67311988864094e-05</v>
+        <v>0.03269737586379051</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0005157852428965271</v>
+        <v>0.01979010924696922</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0006685405387543142</v>
+        <v>0.005297727882862091</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001081461232388392</v>
+        <v>0.02076973766088486</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0001315137778874487</v>
+        <v>0.00905684195458889</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.777343176305294e-05</v>
+        <v>0.002168952487409115</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.377384463325143e-05</v>
+        <v>0.01022745296359062</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0004576830542646348</v>
+        <v>0.03939617425203323</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.571091656340286e-05</v>
+        <v>0.004733562469482422</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0002371254522586241</v>
+        <v>0.001939244568347931</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0002118188131134957</v>
+        <v>0.003243034705519676</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0002067947934847325</v>
+        <v>0.006049733608961105</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001155209756689146</v>
+        <v>0.002603606088086963</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.605634133738931e-05</v>
+        <v>0.0004965115804225206</v>
       </c>
       <c r="CL9" t="n">
-        <v>6.85317900206428e-06</v>
+        <v>0.003280914621427655</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0004627335583791137</v>
+        <v>0.01680555567145348</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0002982202277053148</v>
+        <v>0.06751815974712372</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0002999030402861536</v>
+        <v>0.002423182362690568</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.020453055389225e-05</v>
+        <v>0.03804277628660202</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0003690349985845387</v>
+        <v>0.02797552011907101</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0002239793102489784</v>
+        <v>0.01074084360152483</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.503155181126203e-05</v>
+        <v>0.01079856790602207</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.000191947357961908</v>
+        <v>0.02075517177581787</v>
       </c>
       <c r="CU9" t="n">
-        <v>2.114972085109912e-05</v>
+        <v>0.003609186504036188</v>
       </c>
       <c r="CV9" t="n">
-        <v>7.831552647985518e-05</v>
+        <v>0.00273875892162323</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0002710366970859468</v>
+        <v>0.03710872679948807</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.402823818352772e-05</v>
+        <v>0.005727310664951801</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0003357913519721478</v>
+        <v>0.004837153479456902</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001853438443504274</v>
+        <v>0.004184203688055277</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0002977624535560608</v>
+        <v>0.007396834902465343</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0001052957159117796</v>
+        <v>0.00269135576672852</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.780305294436403e-06</v>
+        <v>0.001176149351522326</v>
       </c>
       <c r="DD9" t="n">
-        <v>6.144073267932981e-05</v>
+        <v>0.002585786394774914</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0001125173876062036</v>
+        <v>0.003638297319412231</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0007207500166259706</v>
+        <v>0.07262679934501648</v>
       </c>
       <c r="DG9" t="n">
-        <v>6.885649781906977e-05</v>
+        <v>0.03471501171588898</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0003897499991580844</v>
+        <v>0.004706596024334431</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0006943329353816807</v>
+        <v>0.02871675416827202</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0001741745218168944</v>
+        <v>0.05177845805883408</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0006663427921012044</v>
+        <v>0.008352109231054783</v>
       </c>
       <c r="DL9" t="n">
-        <v>5.82558277528733e-05</v>
+        <v>0.0351320281624794</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0003367211320437491</v>
+        <v>0.02632488682866096</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0004982901155017316</v>
+        <v>6.879772990942001e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0002873917983379215</v>
+        <v>0.023256441578269</v>
       </c>
       <c r="DP9" t="n">
-        <v>3.235672920709476e-07</v>
+        <v>0.006515787914395332</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0004097339406143874</v>
+        <v>0.02024956420063972</v>
       </c>
       <c r="DR9" t="n">
-        <v>4.247968172421679e-05</v>
+        <v>0.009138628840446472</v>
       </c>
       <c r="DS9" t="n">
-        <v>6.377600220730528e-05</v>
+        <v>0.01523718237876892</v>
       </c>
       <c r="DT9" t="n">
-        <v>3.228071000194177e-05</v>
+        <v>0.01858966052532196</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0002742154756560922</v>
+        <v>0.01703156344592571</v>
       </c>
       <c r="DV9" t="n">
-        <v>5.004416379961185e-06</v>
+        <v>0.002857366343960166</v>
       </c>
       <c r="DW9" t="n">
-        <v>2.670452522579581e-05</v>
+        <v>0.01252347603440285</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0002479137328919023</v>
+        <v>0.01482905726879835</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0003915549023076892</v>
+        <v>0.004467830061912537</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.000108575593912974</v>
+        <v>0.008556436747312546</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0005692500271834433</v>
+        <v>7.273745723068714e-05</v>
       </c>
       <c r="EB9" t="n">
-        <v>8.259275637101382e-05</v>
+        <v>0.003248807275667787</v>
       </c>
       <c r="EC9" t="n">
-        <v>6.885328730277251e-06</v>
+        <v>0.0009202002547681332</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001451725693186745</v>
+        <v>0.01190082170069218</v>
       </c>
       <c r="EE9" t="n">
-        <v>9.447801858186722e-05</v>
+        <v>0.03831960260868073</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0002865852147806436</v>
+        <v>0.007347842678427696</v>
       </c>
       <c r="EG9" t="n">
-        <v>1.479475395171903e-05</v>
+        <v>0.01444865111261606</v>
       </c>
       <c r="EH9" t="n">
-        <v>9.903343016048893e-05</v>
+        <v>0.003821481950581074</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0002014910714933649</v>
+        <v>0.02168959192931652</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.000200173759367317</v>
+        <v>0.004352922085672617</v>
       </c>
       <c r="EK9" t="n">
-        <v>5.997424887027591e-05</v>
+        <v>0.005162985064089298</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001947888522408903</v>
+        <v>0.004969248548150063</v>
       </c>
       <c r="EM9" t="n">
-        <v>9.726863027026411e-06</v>
+        <v>0.01739756390452385</v>
       </c>
       <c r="EN9" t="n">
-        <v>4.049968265462667e-05</v>
+        <v>0.003753413446247578</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0004036282189190388</v>
+        <v>0.008860379457473755</v>
       </c>
       <c r="EP9" t="n">
-        <v>4.351154530013446e-06</v>
+        <v>0.02523499354720116</v>
       </c>
       <c r="EQ9" t="n">
-        <v>3.54099647665862e-05</v>
+        <v>0.007082400843501091</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001391411497024819</v>
+        <v>0.02245271764695644</v>
       </c>
       <c r="ES9" t="n">
-        <v>5.9308124036761e-05</v>
+        <v>0.04622391611337662</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0006215922767296433</v>
+        <v>0.01299383398145437</v>
       </c>
       <c r="EU9" t="n">
-        <v>3.354440195835195e-05</v>
+        <v>0.02457252144813538</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0004046606773044914</v>
+        <v>0.009871096350252628</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0001287963677896187</v>
+        <v>0.0002131804940290749</v>
       </c>
       <c r="EX9" t="n">
-        <v>6.592381396330893e-05</v>
+        <v>0.01058811321854591</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.000241389891016297</v>
+        <v>0.0444653183221817</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0001266420003958046</v>
+        <v>0.001584127894602716</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.000261914829025045</v>
+        <v>0.006022511050105095</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0002124338643625379</v>
+        <v>0.005267594940960407</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0002987226180266589</v>
+        <v>0.006945718545466661</v>
       </c>
       <c r="FD9" t="n">
-        <v>9.495938138570637e-05</v>
+        <v>0.003559896722435951</v>
       </c>
       <c r="FE9" t="n">
-        <v>1.224349216499832e-05</v>
+        <v>0.0009641882497817278</v>
       </c>
       <c r="FF9" t="n">
-        <v>1.738113496685401e-05</v>
+        <v>0.007202658336609602</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0003129024116788059</v>
+        <v>0.02139357849955559</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0004739611758850515</v>
+        <v>0.02344091795384884</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0001939657231559977</v>
+        <v>0.005298004485666752</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0001529532019048929</v>
+        <v>0.01964482292532921</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001008928229566664</v>
+        <v>0.02145030349493027</v>
       </c>
       <c r="FL9" t="n">
-        <v>6.392660725396127e-05</v>
+        <v>0.02851592935621738</v>
       </c>
       <c r="FM9" t="n">
-        <v>5.883031917619519e-05</v>
+        <v>0.01198386028409004</v>
       </c>
       <c r="FN9" t="n">
-        <v>6.299900269368663e-05</v>
+        <v>0.03842839971184731</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0002869789605028927</v>
+        <v>0.02573059499263763</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0003723649133462459</v>
+        <v>0.0285947285592556</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0003478361177258193</v>
+        <v>0.003856380935758352</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0006440583383664489</v>
+        <v>0.01030269917100668</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0004403206403367221</v>
+        <v>0.03285625949501991</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.001073521212674677</v>
+        <v>0.03391337394714355</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0002537959371693432</v>
+        <v>0.03151470795273781</v>
       </c>
       <c r="FV9" t="n">
-        <v>2.870189200621098e-05</v>
+        <v>0.01484773121774197</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0002602071326691657</v>
+        <v>0.04446279257535934</v>
       </c>
       <c r="FX9" t="n">
-        <v>8.010807505343109e-05</v>
+        <v>0.006473056972026825</v>
       </c>
       <c r="FY9" t="n">
-        <v>6.900029256939888e-05</v>
+        <v>0.02574627660214901</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0004929681890644133</v>
+        <v>0.03157409280538559</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0002792950836010277</v>
+        <v>0.01210855506360531</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0003089991223532706</v>
+        <v>0.004808390513062477</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0001516502525191754</v>
+        <v>0.005969501566141844</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0003285098064225167</v>
+        <v>0.01083729416131973</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0001798223966034129</v>
+        <v>0.01504619512706995</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0003822773287538439</v>
+        <v>0.02130776643753052</v>
       </c>
       <c r="GG9" t="n">
-        <v>9.592678543413058e-05</v>
+        <v>0.02328974381089211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0002748302358668298</v>
+        <v>0.002255841158330441</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002547397511079907</v>
+        <v>0.01541935745626688</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001703799061942846</v>
+        <v>0.002870061434805393</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001403443980962038</v>
+        <v>0.01236460916697979</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0004054593737237155</v>
+        <v>0.002525746822357178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0004623816639650613</v>
+        <v>0.01032101735472679</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001313626707997173</v>
+        <v>0.005915889050811529</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0001463842927478254</v>
+        <v>0.00637128809466958</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0002467159065417945</v>
+        <v>0.001289673615247011</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0004109618603251874</v>
+        <v>0.001861677272245288</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001612748834304512</v>
+        <v>0.01547682099044323</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001579678355483338</v>
+        <v>0.005435079801827669</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001530939480289817</v>
+        <v>0.01721873879432678</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0009870126377791166</v>
+        <v>0.00573737733066082</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0008574908133596182</v>
+        <v>0.009139047935605049</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0001553197944303975</v>
+        <v>0.007279175333678722</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001747326750773937</v>
+        <v>0.00197810004465282</v>
       </c>
       <c r="R10" t="n">
-        <v>5.738663458032534e-05</v>
+        <v>0.002028378425166011</v>
       </c>
       <c r="S10" t="n">
-        <v>7.354423723882064e-05</v>
+        <v>0.001225514337420464</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0004177488735876977</v>
+        <v>0.0002712308778427541</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00012911346857436</v>
+        <v>0.0008047719020396471</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0003021442971657962</v>
+        <v>0.0001683842856436968</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0001031862193485722</v>
+        <v>0.001766249071806669</v>
       </c>
       <c r="X10" t="n">
-        <v>0.000340048864018172</v>
+        <v>0.004370907787233591</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002448626910336316</v>
+        <v>0.0007149713928811252</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.172818080405705e-05</v>
+        <v>0.002964731305837631</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.198256308678538e-05</v>
+        <v>0.002725289668887854</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0003140224143862724</v>
+        <v>0.001846602186560631</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0004043196386191994</v>
+        <v>0.001842544646933675</v>
       </c>
       <c r="AD10" t="n">
-        <v>6.047466013114899e-05</v>
+        <v>0.00332117173820734</v>
       </c>
       <c r="AE10" t="n">
-        <v>5.629303996101953e-05</v>
+        <v>4.794984124600887e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0002838277141563594</v>
+        <v>0.001167671754956245</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0001563641562825069</v>
+        <v>0.006781882606446743</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.812818901380524e-05</v>
+        <v>0.000184999720659107</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.452961290255189e-05</v>
+        <v>0.003758796956390142</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.230855094850995e-05</v>
+        <v>0.001535977935418487</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0001333984691882506</v>
+        <v>0.001203439780510962</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0002179658331442624</v>
+        <v>0.005255087278783321</v>
       </c>
       <c r="AM10" t="n">
-        <v>9.249550203094259e-05</v>
+        <v>0.003292635548859835</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0001481987128499895</v>
+        <v>0.002714191330596805</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0003214525931980461</v>
+        <v>0.001628172933124006</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.000324996595736593</v>
+        <v>0.003353998996317387</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.583916835254058e-05</v>
+        <v>0.002316229976713657</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0001920928771141917</v>
+        <v>0.0007963227108120918</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.861108264885843e-05</v>
+        <v>0.001164486282505095</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0003032128734048456</v>
+        <v>0.0005166075425222516</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.002080778358504176</v>
+        <v>0.008458664640784264</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.44086064514704e-05</v>
+        <v>0.003241422353312373</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0002035284123849124</v>
+        <v>0.00607185484841466</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0004159290692768991</v>
+        <v>0.01089680194854736</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0003127572417724878</v>
+        <v>0.007590173278003931</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.132034129928797e-05</v>
+        <v>0.0002183362958021462</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.471073771128431e-05</v>
+        <v>6.123929051682353e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.8221557487268e-05</v>
+        <v>0.001201831735670567</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.833046063547954e-05</v>
+        <v>0.001892966683954</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0004209967155475169</v>
+        <v>0.0002521185670047998</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0003943870542570949</v>
+        <v>0.002922344952821732</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0002906484878621995</v>
+        <v>0.0007758378051221371</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0008184651960618794</v>
+        <v>0.004299501422792673</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0006267077988013625</v>
+        <v>0.001583487959578633</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0003035395930055529</v>
+        <v>0.001737493672408164</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0001676971296546981</v>
+        <v>0.003454908495768905</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.701401874423027e-05</v>
+        <v>0.002083147177472711</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0004923455417156219</v>
+        <v>0.001012349501252174</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0005900162504985929</v>
+        <v>0.0002453652559779584</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.000154618319356814</v>
+        <v>0.0002465260622557253</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0001677844120422378</v>
+        <v>0.002696733921766281</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0004450304550118744</v>
+        <v>0.0002119774871971458</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0002770553110167384</v>
+        <v>0.0002480471157468855</v>
       </c>
       <c r="BR10" t="n">
-        <v>6.272280006669462e-05</v>
+        <v>0.000175911613041535</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0001001998607534915</v>
+        <v>0.001649646670557559</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0001672616053838283</v>
+        <v>0.0007677078247070312</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0002476332592777908</v>
+        <v>3.453352837823331e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0009770285105332732</v>
+        <v>0.006196033209562302</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.820476068649441e-05</v>
+        <v>0.001893482054583728</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0001465776877012104</v>
+        <v>0.006892938166856766</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0001006620732368901</v>
+        <v>0.002322780434042215</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0006779050454497337</v>
+        <v>0.00530196912586689</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.845811417908408e-05</v>
+        <v>0.001086573349311948</v>
       </c>
       <c r="CB10" t="n">
-        <v>8.206309576053172e-05</v>
+        <v>0.0004597897059284151</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.653922223951668e-05</v>
+        <v>0.002324142260476947</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0002090247726300731</v>
+        <v>0.0003041637246496975</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0004236219101585448</v>
+        <v>0.005216012243181467</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0001028910919558257</v>
+        <v>0.0004322601307649165</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0001213825889863074</v>
+        <v>0.004708719439804554</v>
       </c>
       <c r="CH10" t="n">
-        <v>9.977674926631153e-05</v>
+        <v>0.0001546421262901276</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.000164779179613106</v>
+        <v>0.002087467117235065</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0001018253897200339</v>
+        <v>0.00048011977924034</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.401911504217423e-05</v>
+        <v>0.001095100305974483</v>
       </c>
       <c r="CL10" t="n">
-        <v>3.84966770070605e-05</v>
+        <v>6.704984116367996e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0003267147403676063</v>
+        <v>0.0006860315916128457</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0003472024400252849</v>
+        <v>0.002429073443636298</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0002116924442816526</v>
+        <v>0.006409160327166319</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0005713840946555138</v>
+        <v>0.007114757783710957</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0003877149720210582</v>
+        <v>0.0006207182887010276</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0003562625788617879</v>
+        <v>0.002149170730262995</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0001181555126095191</v>
+        <v>0.001103709219023585</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0004298301937524229</v>
+        <v>0.001833907910622656</v>
       </c>
       <c r="CU10" t="n">
-        <v>2.742112519626971e-05</v>
+        <v>0.0007547460263594985</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0001989298471016809</v>
+        <v>0.0002131634100805968</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0003103481139987707</v>
+        <v>0.004997235722839832</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.000133356312289834</v>
+        <v>0.001058126683346927</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0002390425797784701</v>
+        <v>0.005114393308758736</v>
       </c>
       <c r="CZ10" t="n">
-        <v>9.275949560105801e-05</v>
+        <v>0.001177488244138658</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0001657514658290893</v>
+        <v>0.002335058059543371</v>
       </c>
       <c r="DB10" t="n">
-        <v>8.799722127150744e-05</v>
+        <v>0.0007321126759052277</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.128836447605863e-05</v>
+        <v>0.0009454293176531792</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.293580135097727e-05</v>
+        <v>0.0003184325760230422</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0001048077247105539</v>
+        <v>0.0008665719069540501</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0003222417435608804</v>
+        <v>0.004556396976113319</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0001082506205420941</v>
+        <v>0.001137211453169584</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0002993476809933782</v>
+        <v>0.003620503935962915</v>
       </c>
       <c r="DI10" t="n">
-        <v>6.592812860617414e-05</v>
+        <v>0.0005572091322392225</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0001307359052589163</v>
+        <v>0.009789395146071911</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0001295421534450725</v>
+        <v>0.001137500163167715</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0001193568605231121</v>
+        <v>0.00834841001778841</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0001504308165749535</v>
+        <v>0.003571323119103909</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.000413961912272498</v>
+        <v>0.0003312558401376009</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0001392155099892989</v>
+        <v>0.002668745117262006</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0002148750791093335</v>
+        <v>0.0006522417534142733</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0001163788328994997</v>
+        <v>0.001416771905496716</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0001362231123493984</v>
+        <v>9.947696526069194e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0002766206162050366</v>
+        <v>0.001398368971422315</v>
       </c>
       <c r="DT10" t="n">
-        <v>5.073300781077705e-05</v>
+        <v>0.001855816459283233</v>
       </c>
       <c r="DU10" t="n">
-        <v>3.269760782131925e-05</v>
+        <v>0.003487753681838512</v>
       </c>
       <c r="DV10" t="n">
-        <v>3.635764005593956e-05</v>
+        <v>0.006788899190723896</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0001342328905593604</v>
+        <v>3.900815499946475e-06</v>
       </c>
       <c r="DX10" t="n">
-        <v>2.006975591939408e-05</v>
+        <v>0.0003930712700821459</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0002661793259903789</v>
+        <v>0.003392911516129971</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0002023586857831106</v>
+        <v>0.001973224803805351</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0003639575734268874</v>
+        <v>0.0002693824062589556</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0002406978019280359</v>
+        <v>0.005146823357790709</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.774567085201852e-05</v>
+        <v>0.000388209824450314</v>
       </c>
       <c r="ED10" t="n">
-        <v>7.373571133939549e-05</v>
+        <v>0.00738892424851656</v>
       </c>
       <c r="EE10" t="n">
-        <v>3.742543776752427e-05</v>
+        <v>0.007111895363777876</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0001445650414098054</v>
+        <v>0.002489044796675444</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0001787693181540817</v>
+        <v>0.00330287660472095</v>
       </c>
       <c r="EH10" t="n">
-        <v>3.418056076043285e-05</v>
+        <v>0.003123615635558963</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0001908242265926674</v>
+        <v>0.004358403384685516</v>
       </c>
       <c r="EJ10" t="n">
-        <v>8.088034519460052e-05</v>
+        <v>0.0008295620209537446</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0001165518478956074</v>
+        <v>0.001485119806602597</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0001081838709069416</v>
+        <v>0.0001936759217642248</v>
       </c>
       <c r="EM10" t="n">
-        <v>9.483816393185407e-05</v>
+        <v>0.0001340448507107794</v>
       </c>
       <c r="EN10" t="n">
-        <v>2.300156847923063e-05</v>
+        <v>0.000651078182272613</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0002000357198994607</v>
+        <v>0.001391404890455306</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0003076659049838781</v>
+        <v>0.00516553083434701</v>
       </c>
       <c r="EQ10" t="n">
-        <v>7.69775579101406e-05</v>
+        <v>0.0002280283952131867</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0002100988349411637</v>
+        <v>0.003948574885725975</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0001469350245315582</v>
+        <v>0.0009431236539967358</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0006649682181887329</v>
+        <v>0.0005866955034434795</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0001769728260114789</v>
+        <v>0.001582670025527477</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0001440543419448659</v>
+        <v>0.002123817102983594</v>
       </c>
       <c r="EW10" t="n">
-        <v>1.585323116159998e-05</v>
+        <v>0.003878544783219695</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0001379839377477765</v>
+        <v>0.0002040171821136028</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0003331944171804935</v>
+        <v>0.00559340650215745</v>
       </c>
       <c r="EZ10" t="n">
-        <v>3.579217445803806e-05</v>
+        <v>0.0005586445913650095</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0001774880947778001</v>
+        <v>0.005449917167425156</v>
       </c>
       <c r="FB10" t="n">
-        <v>5.815028998767957e-06</v>
+        <v>9.679469803813845e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0002210429811384529</v>
+        <v>0.002247984288260341</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0001037084439303726</v>
+        <v>0.0008937643142417073</v>
       </c>
       <c r="FE10" t="n">
-        <v>1.438763320038561e-05</v>
+        <v>0.001393736689351499</v>
       </c>
       <c r="FF10" t="n">
-        <v>3.949560777982697e-05</v>
+        <v>0.001067422446794808</v>
       </c>
       <c r="FG10" t="n">
-        <v>8.7342421466019e-05</v>
+        <v>0.0002818879438564181</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0001138985317084007</v>
+        <v>0.002534310799092054</v>
       </c>
       <c r="FI10" t="n">
-        <v>1.992441502807196e-05</v>
+        <v>0.0001550178858451545</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0002446250291541219</v>
+        <v>0.002828667405992746</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0001446434325771406</v>
+        <v>0.001111237797886133</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0001689123891992494</v>
+        <v>0.0002217037254013121</v>
       </c>
       <c r="FM10" t="n">
-        <v>4.797590372618288e-05</v>
+        <v>0.001094421138986945</v>
       </c>
       <c r="FN10" t="n">
-        <v>7.642380660399795e-05</v>
+        <v>0.0005373699823394418</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0001779026933945715</v>
+        <v>0.0008860478410497308</v>
       </c>
       <c r="FP10" t="n">
-        <v>2.406279236311093e-06</v>
+        <v>0.002771401777863503</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0001677592081250623</v>
+        <v>0.005942357704043388</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.1459941965295e-05</v>
+        <v>0.004199176095426083</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0004439508193172514</v>
+        <v>0.00494513101875782</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0003449786454439163</v>
+        <v>0.005264018662273884</v>
       </c>
       <c r="FU10" t="n">
-        <v>2.189039150835015e-05</v>
+        <v>0.00222104974091053</v>
       </c>
       <c r="FV10" t="n">
-        <v>8.636793063487858e-05</v>
+        <v>0.0001720126019790769</v>
       </c>
       <c r="FW10" t="n">
-        <v>7.758807623758912e-05</v>
+        <v>0.006231115199625492</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0001890100538730621</v>
+        <v>0.003419855842366815</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.000284538371488452</v>
+        <v>0.001586303347721696</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0002635422279126942</v>
+        <v>0.0006538300076499581</v>
       </c>
       <c r="GA10" t="n">
-        <v>1.717678787827026e-05</v>
+        <v>0.001760449376888573</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0001228266628459096</v>
+        <v>0.004755309782922268</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0001622803829377517</v>
+        <v>0.001089623430743814</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0002987290499731898</v>
+        <v>0.003494134172797203</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0004316896083764732</v>
+        <v>0.002731818240135908</v>
       </c>
       <c r="GF10" t="n">
-        <v>1.145674832514487e-05</v>
+        <v>0.002833810867741704</v>
       </c>
       <c r="GG10" t="n">
-        <v>7.54209904698655e-05</v>
+        <v>0.001777463709004223</v>
       </c>
     </row>
     <row r="11">
@@ -6689,2278 +6689,2278 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.238724206016229e-10</v>
+        <v>2.297121604044605e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>4.064785452673192e-10</v>
+        <v>1.181600879363032e-07</v>
       </c>
       <c r="C12" t="n">
-        <v>1.019161491311316e-10</v>
+        <v>1.670080962412612e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>1.441834207582815e-09</v>
+        <v>3.96367525468122e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>2.359160089504542e-11</v>
+        <v>1.76045400479552e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.497089258117867e-11</v>
+        <v>6.191784507336706e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>3.496294573301917e-11</v>
+        <v>2.147088551396337e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>1.016590422953101e-10</v>
+        <v>3.660974456920485e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>2.203057181127122e-11</v>
+        <v>1.200343202611975e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>3.693582939501283e-10</v>
+        <v>1.261905246963124e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>2.646478314272116e-10</v>
+        <v>1.290091375949487e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>1.118036496716712e-10</v>
+        <v>3.925839209273363e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>6.487541615030068e-10</v>
+        <v>7.939313917404434e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>8.176620491795461e-11</v>
+        <v>6.284691522751018e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>4.328088998306612e-10</v>
+        <v>8.251059568920027e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>2.015022315671189e-10</v>
+        <v>5.544004810786873e-09</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.871831826847028e-10</v>
+        <v>1.120147530286886e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>4.992349242338712e-11</v>
+        <v>3.130859482780579e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>5.425655411062102e-11</v>
+        <v>5.721182194662333e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>3.861958322581849e-11</v>
+        <v>6.999409496444287e-09</v>
       </c>
       <c r="U12" t="n">
-        <v>1.529500553987262e-10</v>
+        <v>3.144184290704288e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.731405470384306e-11</v>
+        <v>3.040808493892655e-09</v>
       </c>
       <c r="W12" t="n">
-        <v>3.054681507741464e-10</v>
+        <v>1.181884812240241e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>2.421347670977791e-11</v>
+        <v>1.578012565062181e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.216440057687066e-10</v>
+        <v>3.896489175758688e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.008049696111129e-11</v>
+        <v>2.259882236899102e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.251605152325808e-10</v>
+        <v>5.383999912567106e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.129977639235946e-10</v>
+        <v>1.503647428791055e-09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.229192581053695e-10</v>
+        <v>1.93308142826254e-08</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.756325541754869e-12</v>
+        <v>6.903691840420834e-09</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.528587617067757e-10</v>
+        <v>4.595928260187065e-08</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.449620506439487e-10</v>
+        <v>4.247316809369295e-08</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.113678481714288e-10</v>
+        <v>5.690892734833142e-08</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.112255218482794e-10</v>
+        <v>8.92260487717067e-09</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.64218499909552e-10</v>
+        <v>4.365118400073698e-08</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.923279393695637e-11</v>
+        <v>6.585796796798604e-09</v>
       </c>
       <c r="AK12" t="n">
-        <v>5.750042109120557e-11</v>
+        <v>6.53711573761484e-09</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.63062771618705e-10</v>
+        <v>2.870781123931465e-08</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.202702798464017e-10</v>
+        <v>3.097772349747174e-08</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.675141937615095e-11</v>
+        <v>2.316925495904343e-08</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.305072799302366e-10</v>
+        <v>7.682535496655873e-09</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.913727926128317e-10</v>
+        <v>1.890747292065953e-08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.972215168954961e-10</v>
+        <v>2.060670922787722e-08</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.439199037722716e-10</v>
+        <v>5.352904786093404e-09</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.510377517499606e-10</v>
+        <v>2.492629214145836e-09</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.624360368435163e-13</v>
+        <v>4.081900151220452e-09</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.391239869094292e-11</v>
+        <v>9.921647858845972e-08</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.854413647256919e-11</v>
+        <v>5.103807865225463e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.198976970101967e-10</v>
+        <v>1.289435402895833e-08</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.193430423929165e-11</v>
+        <v>9.570130998781678e-08</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.129482421097677e-11</v>
+        <v>8.305546828069055e-08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.736987498279774e-10</v>
+        <v>2.803939302964409e-10</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.489469103610475e-10</v>
+        <v>8.763006320577915e-09</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.67697261527411e-10</v>
+        <v>2.911191288035297e-10</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.808582728024533e-10</v>
+        <v>1.496696100389272e-08</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.493892923398192e-11</v>
+        <v>3.463770781308995e-08</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.368290534324416e-11</v>
+        <v>1.513171810074709e-08</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.957391772757006e-11</v>
+        <v>2.958880251924256e-09</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.785472101393907e-11</v>
+        <v>6.574695987637824e-08</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.848174887747916e-11</v>
+        <v>1.698506668645905e-09</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.322219139732184e-10</v>
+        <v>9.331277084356771e-09</v>
       </c>
       <c r="BJ12" t="n">
-        <v>6.117622519674626e-10</v>
+        <v>4.376724760390971e-08</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.371595545474058e-11</v>
+        <v>1.141583894082032e-08</v>
       </c>
       <c r="BL12" t="n">
-        <v>4.502867523292764e-11</v>
+        <v>7.449107997103965e-11</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.494273177415906e-10</v>
+        <v>9.319482074943153e-09</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.160540205602523e-10</v>
+        <v>1.674407101859288e-08</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.269455651708995e-10</v>
+        <v>8.736348533489036e-09</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.98562971620575e-10</v>
+        <v>3.297253670098144e-08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.114009245435255e-10</v>
+        <v>1.274256478112079e-09</v>
       </c>
       <c r="BR12" t="n">
-        <v>2.013994873650837e-11</v>
+        <v>1.41734428638074e-08</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.540762392144735e-11</v>
+        <v>1.697279294887721e-08</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.686087794527396e-11</v>
+        <v>1.455730203048233e-09</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.134329601417463e-12</v>
+        <v>1.277464711790799e-08</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.164693144323664e-11</v>
+        <v>6.515632833270502e-08</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.757133213022072e-11</v>
+        <v>3.362570311082891e-08</v>
       </c>
       <c r="BX12" t="n">
-        <v>2.791622211173461e-10</v>
+        <v>9.230307185248421e-09</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.712552044619287e-10</v>
+        <v>2.049989733521329e-09</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.861306664352469e-10</v>
+        <v>3.90728978061361e-08</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.309528956967455e-10</v>
+        <v>3.575469875727322e-08</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.371311536546571e-10</v>
+        <v>6.577472344559965e-09</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.469724424969399e-10</v>
+        <v>1.257059167869556e-08</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.625549777590663e-11</v>
+        <v>5.538611236310942e-10</v>
       </c>
       <c r="CE12" t="n">
-        <v>7.269754243033333e-11</v>
+        <v>4.218581750592421e-08</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.57546115042706e-10</v>
+        <v>3.833712014511548e-09</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.452200443230467e-10</v>
+        <v>1.385848413804069e-08</v>
       </c>
       <c r="CH12" t="n">
-        <v>7.866551854363024e-11</v>
+        <v>1.545373073952305e-08</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.686658451793832e-11</v>
+        <v>1.525211246189428e-08</v>
       </c>
       <c r="CJ12" t="n">
-        <v>8.800968287481226e-11</v>
+        <v>7.882225538935472e-09</v>
       </c>
       <c r="CK12" t="n">
-        <v>6.457055029551739e-11</v>
+        <v>4.309247403355698e-10</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.853548980967901e-10</v>
+        <v>7.796878698229648e-10</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.331854071473515e-11</v>
+        <v>5.017333037926619e-08</v>
       </c>
       <c r="CN12" t="n">
-        <v>3.159635331151378e-10</v>
+        <v>7.227616549698723e-08</v>
       </c>
       <c r="CO12" t="n">
-        <v>5.934079616576327e-11</v>
+        <v>6.356316362143843e-08</v>
       </c>
       <c r="CP12" t="n">
-        <v>3.435401685347728e-10</v>
+        <v>1.277429539925379e-08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.73475289688696e-10</v>
+        <v>1.473847177635434e-08</v>
       </c>
       <c r="CR12" t="n">
-        <v>2.851165414874401e-10</v>
+        <v>2.399770160366188e-08</v>
       </c>
       <c r="CS12" t="n">
-        <v>1.81344703142905e-10</v>
+        <v>3.379483715093556e-08</v>
       </c>
       <c r="CT12" t="n">
-        <v>5.142962167248299e-10</v>
+        <v>1.823296402747587e-09</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.122539474568418e-11</v>
+        <v>3.904634837681442e-09</v>
       </c>
       <c r="CV12" t="n">
-        <v>3.385300373359712e-11</v>
+        <v>1.346560862813817e-09</v>
       </c>
       <c r="CW12" t="n">
-        <v>8.184809774380852e-11</v>
+        <v>3.681608973238326e-08</v>
       </c>
       <c r="CX12" t="n">
-        <v>9.000437894979285e-11</v>
+        <v>3.650109769992582e-09</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.556513056806153e-10</v>
+        <v>1.870391486136214e-08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>8.569791404289262e-11</v>
+        <v>2.313441704870911e-08</v>
       </c>
       <c r="DA12" t="n">
-        <v>4.596926311828398e-11</v>
+        <v>1.48527465881898e-08</v>
       </c>
       <c r="DB12" t="n">
-        <v>8.135903062367333e-11</v>
+        <v>1.153863848912806e-08</v>
       </c>
       <c r="DC12" t="n">
-        <v>7.610761326715121e-11</v>
+        <v>2.115089436927065e-09</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.384275333249363e-10</v>
+        <v>3.118997726758721e-09</v>
       </c>
       <c r="DE12" t="n">
-        <v>7.995514667014092e-11</v>
+        <v>1.763853951786132e-08</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.897481421459958e-10</v>
+        <v>1.38649092207288e-09</v>
       </c>
       <c r="DG12" t="n">
-        <v>5.576450412547729e-10</v>
+        <v>1.808064808983545e-09</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.209518929456976e-09</v>
+        <v>1.638664848258031e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>4.526544972183189e-10</v>
+        <v>3.808171111785441e-09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>4.620236832009184e-11</v>
+        <v>5.15421945124217e-08</v>
       </c>
       <c r="DK12" t="n">
-        <v>9.596962807778553e-11</v>
+        <v>7.02762559257053e-09</v>
       </c>
       <c r="DL12" t="n">
-        <v>7.391549039503786e-10</v>
+        <v>5.768212218981716e-08</v>
       </c>
       <c r="DM12" t="n">
-        <v>6.795578683105319e-11</v>
+        <v>1.177060848789324e-08</v>
       </c>
       <c r="DN12" t="n">
-        <v>5.808499514703414e-11</v>
+        <v>1.366709412309319e-08</v>
       </c>
       <c r="DO12" t="n">
-        <v>4.504610573441425e-11</v>
+        <v>2.640511098661591e-08</v>
       </c>
       <c r="DP12" t="n">
-        <v>2.338699511827969e-10</v>
+        <v>3.451958718869719e-10</v>
       </c>
       <c r="DQ12" t="n">
-        <v>1.280833425432171e-11</v>
+        <v>1.598704280070251e-08</v>
       </c>
       <c r="DR12" t="n">
-        <v>1.948538969065439e-10</v>
+        <v>1.505868318929515e-08</v>
       </c>
       <c r="DS12" t="n">
-        <v>1.71001934834436e-10</v>
+        <v>1.331774335255886e-08</v>
       </c>
       <c r="DT12" t="n">
-        <v>3.349696908738764e-11</v>
+        <v>3.11014076714855e-08</v>
       </c>
       <c r="DU12" t="n">
-        <v>5.801633479185497e-11</v>
+        <v>3.217256683285541e-09</v>
       </c>
       <c r="DV12" t="n">
-        <v>3.930044900624097e-10</v>
+        <v>7.373925914322399e-09</v>
       </c>
       <c r="DW12" t="n">
-        <v>1.089625820127615e-10</v>
+        <v>4.213491777704803e-10</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.155497503235736e-10</v>
+        <v>2.207853988522857e-08</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.468289739265828e-10</v>
+        <v>2.65623985029606e-08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.432517712928743e-11</v>
+        <v>2.524967790407118e-09</v>
       </c>
       <c r="EA12" t="n">
-        <v>2.000291182691072e-10</v>
+        <v>4.790078733662995e-08</v>
       </c>
       <c r="EB12" t="n">
-        <v>3.566660577991598e-10</v>
+        <v>1.580386133070988e-08</v>
       </c>
       <c r="EC12" t="n">
-        <v>7.854650263539042e-11</v>
+        <v>2.622453143530379e-09</v>
       </c>
       <c r="ED12" t="n">
-        <v>6.313695399828845e-11</v>
+        <v>3.357974165396627e-08</v>
       </c>
       <c r="EE12" t="n">
-        <v>1.630638332694723e-11</v>
+        <v>5.614069564785495e-08</v>
       </c>
       <c r="EF12" t="n">
-        <v>1.901305501927908e-12</v>
+        <v>2.310362123836285e-09</v>
       </c>
       <c r="EG12" t="n">
-        <v>4.601710679175142e-11</v>
+        <v>1.388066106500219e-09</v>
       </c>
       <c r="EH12" t="n">
-        <v>8.582990221328579e-12</v>
+        <v>2.426750178585735e-08</v>
       </c>
       <c r="EI12" t="n">
-        <v>1.54232238092078e-10</v>
+        <v>1.463129173373545e-08</v>
       </c>
       <c r="EJ12" t="n">
-        <v>9.941372725030817e-11</v>
+        <v>1.78327237421172e-08</v>
       </c>
       <c r="EK12" t="n">
-        <v>6.478276248778059e-11</v>
+        <v>1.3588763891903e-08</v>
       </c>
       <c r="EL12" t="n">
-        <v>1.2550940842182e-10</v>
+        <v>1.547002526081087e-08</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.753716616370582e-11</v>
+        <v>3.761701616866731e-09</v>
       </c>
       <c r="EN12" t="n">
-        <v>1.083606676610671e-10</v>
+        <v>1.711897468226198e-08</v>
       </c>
       <c r="EO12" t="n">
-        <v>3.199207565529605e-11</v>
+        <v>7.044084426865993e-09</v>
       </c>
       <c r="EP12" t="n">
-        <v>1.347553735264739e-10</v>
+        <v>3.366347911537559e-08</v>
       </c>
       <c r="EQ12" t="n">
-        <v>1.687335687838853e-10</v>
+        <v>1.170955954421515e-08</v>
       </c>
       <c r="ER12" t="n">
-        <v>4.319289717558128e-12</v>
+        <v>8.363512105091786e-10</v>
       </c>
       <c r="ES12" t="n">
-        <v>3.965485995127693e-10</v>
+        <v>2.528432929693736e-08</v>
       </c>
       <c r="ET12" t="n">
-        <v>5.028782251725872e-11</v>
+        <v>8.701894316232028e-09</v>
       </c>
       <c r="EU12" t="n">
-        <v>9.230324837794512e-12</v>
+        <v>3.042404106423646e-09</v>
       </c>
       <c r="EV12" t="n">
-        <v>3.834980388806031e-10</v>
+        <v>1.157940054952178e-08</v>
       </c>
       <c r="EW12" t="n">
-        <v>8.95196416994537e-11</v>
+        <v>2.098400031513847e-08</v>
       </c>
       <c r="EX12" t="n">
-        <v>1.58780766312816e-11</v>
+        <v>4.405727449530161e-10</v>
       </c>
       <c r="EY12" t="n">
-        <v>6.294596788247731e-11</v>
+        <v>4.125597641291279e-08</v>
       </c>
       <c r="EZ12" t="n">
-        <v>1.293141843605738e-10</v>
+        <v>1.175060271307871e-09</v>
       </c>
       <c r="FA12" t="n">
-        <v>2.060972226214375e-10</v>
+        <v>1.717780051535556e-08</v>
       </c>
       <c r="FB12" t="n">
-        <v>5.565567451348841e-11</v>
+        <v>1.0658578020184e-08</v>
       </c>
       <c r="FC12" t="n">
-        <v>2.200677834407472e-11</v>
+        <v>1.227747592480455e-08</v>
       </c>
       <c r="FD12" t="n">
-        <v>9.776033454977906e-11</v>
+        <v>8.70798988472643e-11</v>
       </c>
       <c r="FE12" t="n">
-        <v>6.38051417256591e-11</v>
+        <v>2.964678280648059e-09</v>
       </c>
       <c r="FF12" t="n">
-        <v>1.841106156419414e-10</v>
+        <v>1.095579627019561e-08</v>
       </c>
       <c r="FG12" t="n">
-        <v>6.99423366445906e-11</v>
+        <v>1.423000028921706e-08</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.691248391333389e-10</v>
+        <v>8.347751823123417e-09</v>
       </c>
       <c r="FI12" t="n">
-        <v>3.527108050072059e-10</v>
+        <v>1.599128829354868e-08</v>
       </c>
       <c r="FJ12" t="n">
-        <v>3.986361241103964e-10</v>
+        <v>1.580811925805392e-08</v>
       </c>
       <c r="FK12" t="n">
-        <v>1.963746526500998e-10</v>
+        <v>2.2677395516979e-09</v>
       </c>
       <c r="FL12" t="n">
-        <v>3.48845084763294e-11</v>
+        <v>1.364838375650379e-08</v>
       </c>
       <c r="FM12" t="n">
-        <v>2.205799293220068e-10</v>
+        <v>1.472126509582949e-08</v>
       </c>
       <c r="FN12" t="n">
-        <v>1.605411498184495e-10</v>
+        <v>1.14510765314435e-08</v>
       </c>
       <c r="FO12" t="n">
-        <v>4.670131295569924e-11</v>
+        <v>5.39044862080118e-08</v>
       </c>
       <c r="FP12" t="n">
-        <v>4.187921537335271e-11</v>
+        <v>3.350176669414395e-08</v>
       </c>
       <c r="FQ12" t="n">
-        <v>5.152882981418472e-11</v>
+        <v>4.981421497518568e-08</v>
       </c>
       <c r="FR12" t="n">
-        <v>3.065554060599496e-11</v>
+        <v>3.057807873574347e-08</v>
       </c>
       <c r="FS12" t="n">
-        <v>6.828856924379068e-12</v>
+        <v>2.081159600209048e-08</v>
       </c>
       <c r="FT12" t="n">
-        <v>1.848987629671228e-10</v>
+        <v>5.932314195433719e-08</v>
       </c>
       <c r="FU12" t="n">
-        <v>9.947792589670712e-12</v>
+        <v>3.969169881656853e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>1.301484961468979e-13</v>
+        <v>3.187168218232728e-08</v>
       </c>
       <c r="FW12" t="n">
-        <v>1.293096324461729e-10</v>
+        <v>4.050915691777845e-08</v>
       </c>
       <c r="FX12" t="n">
-        <v>2.645821409186233e-11</v>
+        <v>7.127479939583736e-09</v>
       </c>
       <c r="FY12" t="n">
-        <v>2.576184543467974e-10</v>
+        <v>9.930263278334905e-10</v>
       </c>
       <c r="FZ12" t="n">
-        <v>1.784262182447094e-10</v>
+        <v>2.615841765418736e-09</v>
       </c>
       <c r="GA12" t="n">
-        <v>3.064268977448492e-11</v>
+        <v>2.198853366053299e-08</v>
       </c>
       <c r="GB12" t="n">
-        <v>3.635147391434224e-11</v>
+        <v>2.174359536866177e-08</v>
       </c>
       <c r="GC12" t="n">
-        <v>2.269127385989833e-10</v>
+        <v>1.98906562332013e-08</v>
       </c>
       <c r="GD12" t="n">
-        <v>4.266691167043035e-11</v>
+        <v>3.842909990225962e-08</v>
       </c>
       <c r="GE12" t="n">
-        <v>5.567897809477529e-10</v>
+        <v>4.669448472327531e-08</v>
       </c>
       <c r="GF12" t="n">
-        <v>1.510939429127944e-10</v>
+        <v>1.908758484603368e-09</v>
       </c>
       <c r="GG12" t="n">
-        <v>3.0107388804268e-10</v>
+        <v>2.459009351696295e-08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0005531011847779155</v>
+        <v>0.008366726338863373</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00362528907135129</v>
+        <v>0.04433266073465347</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001047136101988144</v>
+        <v>0.0476982481777668</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00191434274893254</v>
+        <v>0.01346485782414675</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0003132206620648503</v>
+        <v>0.02974815666675568</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003196629928424954</v>
+        <v>0.05323534086346626</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002103058941429481</v>
+        <v>0.01268789079040289</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008186909253709018</v>
+        <v>0.04924879223108292</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000183352647582069</v>
+        <v>0.00356050580739975</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0008261582115665078</v>
+        <v>0.01436241623014212</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00299414386972785</v>
+        <v>0.1260486841201782</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0002044920984189957</v>
+        <v>0.04004011675715446</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001925593474879861</v>
+        <v>0.01024734321981668</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0004485188110265881</v>
+        <v>0.04936583340167999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00331336073577404</v>
+        <v>0.07832098007202148</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0003670458972919732</v>
+        <v>0.04840818047523499</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.335152572020888e-05</v>
+        <v>0.003273181151598692</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0001155285281129181</v>
+        <v>0.005972533952444792</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002302873908774927</v>
+        <v>0.01512652728706598</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0005460306419990957</v>
+        <v>7.346458733081818e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>7.52300547901541e-06</v>
+        <v>0.001280649099498987</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0005089603364467621</v>
+        <v>0.02974164858460426</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0001060158392647281</v>
+        <v>0.03477873653173447</v>
       </c>
       <c r="X13" t="n">
-        <v>6.320312240859494e-05</v>
+        <v>0.01455342769622803</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0002867936855182052</v>
+        <v>0.01400715950876474</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.644621079321951e-05</v>
+        <v>0.04713165387511253</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0003982579510193318</v>
+        <v>0.01479696948081255</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.766272756271064e-05</v>
+        <v>0.04481573402881622</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0003180743951816112</v>
+        <v>0.001738655846565962</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0002167767088394612</v>
+        <v>0.01417894847691059</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0004399904864840209</v>
+        <v>0.002252937061712146</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.000195693937712349</v>
+        <v>0.06862040609121323</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0001128786025219597</v>
+        <v>0.01357302535325289</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0007012803107500076</v>
+        <v>0.02626373991370201</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0001834112190408632</v>
+        <v>0.05023852363228798</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0002217896108049899</v>
+        <v>0.007149365730583668</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0004067622940056026</v>
+        <v>0.01256846077740192</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.000575434707570821</v>
+        <v>0.000909857451915741</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0001489442074671388</v>
+        <v>0.003399191424250603</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.208758663386106e-05</v>
+        <v>0.0101805878803134</v>
       </c>
       <c r="AO13" t="n">
-        <v>7.780576561344787e-05</v>
+        <v>0.02700704149901867</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0004946758272126317</v>
+        <v>0.001568440464325249</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0002220882452093065</v>
+        <v>0.01626927219331264</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.30567786982283e-06</v>
+        <v>0.0413389690220356</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0003692434402182698</v>
+        <v>0.004623338580131531</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0005135845276527107</v>
+        <v>0.005087803117930889</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.002721202559769154</v>
+        <v>0.1191699877381325</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0003084950731135905</v>
+        <v>0.0268159918487072</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0003858261043205857</v>
+        <v>0.008245257660746574</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0007401896291412413</v>
+        <v>0.03210487216711044</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.001625556615181267</v>
+        <v>0.05976209416985512</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.000391719862818718</v>
+        <v>0.00888175331056118</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0007004695944488049</v>
+        <v>0.01516449078917503</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0004734638496302068</v>
+        <v>0.005992304533720016</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.000381037563784048</v>
+        <v>0.02340552024543285</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0007167697185650468</v>
+        <v>0.01554835215210915</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0008419638616032898</v>
+        <v>0.001112384721636772</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0009401847491972148</v>
+        <v>0.0211401954293251</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001193784293718636</v>
+        <v>0.02447527460753918</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.001184621476568282</v>
+        <v>0.01351162418723106</v>
       </c>
       <c r="BI13" t="n">
-        <v>8.501033880747855e-05</v>
+        <v>0.01590888202190399</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0007418434252031147</v>
+        <v>0.05025136098265648</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.524299194803461e-05</v>
+        <v>0.01855229213833809</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0002392902242718264</v>
+        <v>0.01904138177633286</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0008573115337640047</v>
+        <v>0.05475518107414246</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0002665160282049328</v>
+        <v>0.004878135863691568</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0008197749266400933</v>
+        <v>0.02319318801164627</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.000655703479424119</v>
+        <v>0.03176965937018394</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.018147461058106e-05</v>
+        <v>0.0007944523822516203</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0005778798367828131</v>
+        <v>0.01192890293896198</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.705962293082848e-05</v>
+        <v>0.02848970517516136</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.335832975106314e-05</v>
+        <v>0.0005109596531838179</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0002534226223360747</v>
+        <v>0.008558966219425201</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.001366663258522749</v>
+        <v>0.05616727843880653</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.916247467510402e-05</v>
+        <v>0.01216430217027664</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0001222840946866199</v>
+        <v>0.03631526231765747</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0001342854666290805</v>
+        <v>0.02474358677864075</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0003008756320923567</v>
+        <v>0.0203249491751194</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.000566161994356662</v>
+        <v>0.009898615069687366</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0004038803454022855</v>
+        <v>0.02507880143821239</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0003759682876989245</v>
+        <v>0.0001810017856769264</v>
       </c>
       <c r="CD13" t="n">
-        <v>8.368556154891849e-05</v>
+        <v>0.01441378518939018</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0006943652988411486</v>
+        <v>0.01546125765889883</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.000294652912998572</v>
+        <v>0.01357083488255739</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0004306017654016614</v>
+        <v>0.0003348815080244094</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0002177262504119426</v>
+        <v>0.01609377004206181</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0005384949618019164</v>
+        <v>0.02170893549919128</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0001834806462284178</v>
+        <v>0.009508880786597729</v>
       </c>
       <c r="CK13" t="n">
-        <v>6.932466203579679e-05</v>
+        <v>0.004723732359707355</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0002168817009078339</v>
+        <v>0.004605364985764027</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.00052851956570521</v>
+        <v>0.001436576247215271</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0004568486474454403</v>
+        <v>0.07091566920280457</v>
       </c>
       <c r="CO13" t="n">
-        <v>7.852971612010151e-05</v>
+        <v>0.006290078163146973</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0005005650455132127</v>
+        <v>0.05186638236045837</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0002011025790125132</v>
+        <v>0.02743317931890488</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0001335072593064979</v>
+        <v>0.0258591752499342</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0002063280699076131</v>
+        <v>0.02448279038071632</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.000519127061124891</v>
+        <v>0.003454873338341713</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001465051318518817</v>
+        <v>0.006883031688630581</v>
       </c>
       <c r="CV13" t="n">
-        <v>4.779230584972538e-05</v>
+        <v>0.01057044602930546</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0005235336720943451</v>
+        <v>0.01339286472648382</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0002475979854352772</v>
+        <v>0.01056359615176916</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0005926906014792621</v>
+        <v>0.005357545334845781</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0001489756541559473</v>
+        <v>0.005998383741825819</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0005191586678847671</v>
+        <v>0.02246605418622494</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0002607469505164772</v>
+        <v>0.00257856328971684</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.00034335270174779</v>
+        <v>0.008195015601813793</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0001146711510955356</v>
+        <v>0.007894418202340603</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0002754595188889652</v>
+        <v>0.02587795257568359</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.00119916838593781</v>
+        <v>0.02263647690415382</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0001492756273364648</v>
+        <v>0.0400548055768013</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.001043174299411476</v>
+        <v>0.03976508229970932</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0002036827645497397</v>
+        <v>0.04874539747834206</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0001341928145848215</v>
+        <v>0.01804445683956146</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0007909850683063269</v>
+        <v>0.03207360953092575</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0007833083509467542</v>
+        <v>0.01575967483222485</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0004135882190894336</v>
+        <v>0.005446530878543854</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0002913306234404445</v>
+        <v>0.01860646530985832</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0003582238568924367</v>
+        <v>0.02894255518913269</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0004414330469444394</v>
+        <v>0.0007601100951433182</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0006231306469999254</v>
+        <v>0.03445357829332352</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.78833717352245e-05</v>
+        <v>0.03457764908671379</v>
       </c>
       <c r="DS13" t="n">
-        <v>6.145602674223483e-05</v>
+        <v>0.01074429787695408</v>
       </c>
       <c r="DT13" t="n">
-        <v>4.208366954117082e-05</v>
+        <v>0.006196692585945129</v>
       </c>
       <c r="DU13" t="n">
-        <v>9.512847464065999e-05</v>
+        <v>0.0487060584127903</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0002852985635399818</v>
+        <v>0.003934488631784916</v>
       </c>
       <c r="DW13" t="n">
-        <v>5.497300298884511e-05</v>
+        <v>0.02941517345607281</v>
       </c>
       <c r="DX13" t="n">
-        <v>6.032748206052929e-05</v>
+        <v>0.01584427244961262</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0003013024688698351</v>
+        <v>0.02117625810205936</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.688452125061303e-05</v>
+        <v>0.0008492707274854183</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.000103845028206706</v>
+        <v>0.002327945549041033</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0002243412018287927</v>
+        <v>0.0269167572259903</v>
       </c>
       <c r="EC13" t="n">
-        <v>7.232128700707108e-05</v>
+        <v>0.003401349298655987</v>
       </c>
       <c r="ED13" t="n">
-        <v>7.397886656690389e-05</v>
+        <v>0.00781581923365593</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0002984414750244468</v>
+        <v>0.01611637696623802</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0001745953195495531</v>
+        <v>0.006709561683237553</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0002138932031812146</v>
+        <v>0.01322287134826183</v>
       </c>
       <c r="EH13" t="n">
-        <v>4.951035953126848e-05</v>
+        <v>0.007998472079634666</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0001626324228709564</v>
+        <v>0.01756997965276241</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001512668677605689</v>
+        <v>0.008993867784738541</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0004175609210506082</v>
+        <v>0.02402213029563427</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0003056106506846845</v>
+        <v>0.004771380219608545</v>
       </c>
       <c r="EM13" t="n">
-        <v>9.829772170633078e-05</v>
+        <v>0.01438692305237055</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0001615532382857054</v>
+        <v>0.008201242424547672</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0002862208057194948</v>
+        <v>0.004809591919183731</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0001874473091447726</v>
+        <v>0.006426163949072361</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0001738429418765008</v>
+        <v>0.009048382751643658</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0002685307408683002</v>
+        <v>0.02217799425125122</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0002255287836305797</v>
+        <v>0.002258503576740623</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0006983275525271893</v>
+        <v>0.007987761870026588</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0002513341314624995</v>
+        <v>0.009461350739002228</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0005173356621526182</v>
+        <v>0.005157512612640858</v>
       </c>
       <c r="EW13" t="n">
-        <v>1.998383595491759e-05</v>
+        <v>0.01082474458962679</v>
       </c>
       <c r="EX13" t="n">
-        <v>7.216902304207906e-05</v>
+        <v>0.01389111578464508</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.000485931639559567</v>
+        <v>0.01817530393600464</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001452969299862161</v>
+        <v>0.01309250853955746</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0003975777071900666</v>
+        <v>0.0004266448377165943</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001518618810223415</v>
+        <v>0.007102289237082005</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0005122433649376035</v>
+        <v>0.02445349842309952</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0002944866428151727</v>
+        <v>0.01205363590270281</v>
       </c>
       <c r="FE13" t="n">
-        <v>7.670938066439703e-05</v>
+        <v>0.0001483712112531066</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0002595475525595248</v>
+        <v>0.007488544564694166</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0002107636537402868</v>
+        <v>0.02194341085851192</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0003886354097630829</v>
+        <v>0.003786810440942645</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0002129164786310866</v>
+        <v>0.003943126648664474</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0002578881976660341</v>
+        <v>0.02415416575968266</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001483218802604824</v>
+        <v>0.007319283671677113</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0001243357692146674</v>
+        <v>0.002362373284995556</v>
       </c>
       <c r="FM13" t="n">
-        <v>5.657807923853397e-05</v>
+        <v>0.0212795939296484</v>
       </c>
       <c r="FN13" t="n">
-        <v>7.971017475938424e-05</v>
+        <v>0.03110057674348354</v>
       </c>
       <c r="FO13" t="n">
-        <v>7.684493175474927e-05</v>
+        <v>0.009702463634312153</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0003894041874445975</v>
+        <v>0.01000836864113808</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0001278280251426622</v>
+        <v>0.04277069866657257</v>
       </c>
       <c r="FR13" t="n">
-        <v>4.91371683892794e-05</v>
+        <v>0.0216322299093008</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0003756641817744821</v>
+        <v>0.02408947795629501</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.001548519590869546</v>
+        <v>0.01786105334758759</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0003704233677126467</v>
+        <v>0.02550881914794445</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0001750358933350071</v>
+        <v>0.02738267928361893</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0004871929413639009</v>
+        <v>0.008927969262003899</v>
       </c>
       <c r="FX13" t="n">
-        <v>9.354714711662382e-05</v>
+        <v>0.01873522438108921</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0004175776266492903</v>
+        <v>0.007247497327625751</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0004009910335298628</v>
+        <v>0.02031967975199223</v>
       </c>
       <c r="GA13" t="n">
-        <v>3.827709952020086e-05</v>
+        <v>0.002790327183902264</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0005152195226401091</v>
+        <v>0.01460337266325951</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0002328344562556595</v>
+        <v>0.01806374453008175</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0003741009277291596</v>
+        <v>0.000615636701695621</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.00116399850230664</v>
+        <v>0.006448299624025822</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.000547956267837435</v>
+        <v>0.008805951103568077</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0004109058936592191</v>
+        <v>0.02104090712964535</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.001070183236151934</v>
+        <v>3.064272732444806e-06</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0005242241895757616</v>
+        <v>6.250986916711554e-05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002682355465367436</v>
+        <v>0.0001050735445460305</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002169081708416343</v>
+        <v>0.0001358952140435576</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001418792875483632</v>
+        <v>2.275431688758545e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0005740289343520999</v>
+        <v>5.132637306815013e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005921581177972257</v>
+        <v>2.928323920059483e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003173980803694576</v>
+        <v>4.636339508579113e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0005317417089827359</v>
+        <v>9.072011744137853e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0008868294535204768</v>
+        <v>1.967424213944469e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005035190843045712</v>
+        <v>6.69896398903802e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002056797035038471</v>
+        <v>0.0001432348362868652</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002275720005854964</v>
+        <v>0.0001777704455889761</v>
       </c>
       <c r="N14" t="n">
-        <v>5.615689588012174e-05</v>
+        <v>2.935770135081839e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006294577615335584</v>
+        <v>7.641527918167412e-05</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0003370787017047405</v>
+        <v>2.52470636041835e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25014620507136e-05</v>
+        <v>9.57212396315299e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0009769813623279333</v>
+        <v>5.232715921010822e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003254271578043699</v>
+        <v>1.750049523252528e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0004239756963215768</v>
+        <v>1.677927684795577e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0004135834751650691</v>
+        <v>2.308803959749639e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0004531383456196636</v>
+        <v>2.035575380432419e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0003475963312666863</v>
+        <v>2.89886102109449e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0001731461670715362</v>
+        <v>3.722476685652509e-05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0003700978995766491</v>
+        <v>1.975683335331269e-05</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0002574885438662022</v>
+        <v>1.046416582539678e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.045624518766999e-05</v>
+        <v>3.300313983345404e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0008794124587439001</v>
+        <v>2.337867044843733e-05</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.927968934178352e-05</v>
+        <v>9.259131729777437e-06</v>
       </c>
       <c r="AD14" t="n">
-        <v>9.643657540436834e-05</v>
+        <v>9.450022844248451e-06</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0009182635694742203</v>
+        <v>6.076493446016684e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0007593284244649112</v>
+        <v>2.146347833331674e-05</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.352655767230317e-06</v>
+        <v>2.713189132919069e-06</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.335808625910431e-05</v>
+        <v>6.055239282432012e-06</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0003171199641656131</v>
+        <v>4.169986277702264e-05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.000360210775397718</v>
+        <v>2.189804035879206e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0002627731009852141</v>
+        <v>7.439700311806519e-06</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.687078762799501e-05</v>
+        <v>2.805037183861714e-06</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.150512591470033e-05</v>
+        <v>2.649314774316736e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001670619240030646</v>
+        <v>3.19922219205182e-05</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0006517691072076559</v>
+        <v>3.410721183172427e-05</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0001562025572638959</v>
+        <v>5.502122803591192e-06</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0002959671546705067</v>
+        <v>2.582611705292948e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.092978921718895e-05</v>
+        <v>2.620771192596294e-05</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001990087330341339</v>
+        <v>3.99879427277483e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0008846773416735232</v>
+        <v>2.270151526317932e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0009676560875959694</v>
+        <v>4.592475306708366e-07</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.001500040758401155</v>
+        <v>0.0001509800058556721</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.001869140774942935</v>
+        <v>0.000105282713775523</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0003433837846387178</v>
+        <v>8.342304681718815e-06</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.000686434970702976</v>
+        <v>7.996799831744283e-05</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0004373713163658977</v>
+        <v>7.246168388519436e-05</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0005069856415502727</v>
+        <v>2.40375902649248e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0004045004025101662</v>
+        <v>7.154539343900979e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0007965218974277377</v>
+        <v>2.025055073318072e-05</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.001543106860481203</v>
+        <v>1.499587415310089e-05</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0003453704121056944</v>
+        <v>2.556304025347345e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0007806475041434169</v>
+        <v>1.718144994811155e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0006162742502056062</v>
+        <v>1.367225468129618e-05</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.001003530924208462</v>
+        <v>2.653880073921755e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0006337865488603711</v>
+        <v>5.897433584323153e-05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>7.83940777182579e-07</v>
+        <v>5.789082570117898e-05</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0008492241031490266</v>
+        <v>4.756102498504333e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>4.008491669083014e-05</v>
+        <v>4.454788358998485e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0005365857505239546</v>
+        <v>3.929366357624531e-05</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.000208970857784152</v>
+        <v>1.209423498949036e-05</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.969223689637147e-05</v>
+        <v>2.530615347495768e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0005491788615472615</v>
+        <v>3.285471393610351e-05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.463518704753369e-05</v>
+        <v>1.139606411015848e-05</v>
       </c>
       <c r="BR14" t="n">
-        <v>2.272996061947197e-05</v>
+        <v>1.499720110587077e-05</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0002855139318853617</v>
+        <v>6.739336822647601e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0002031073527177796</v>
+        <v>1.271114615519764e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.000238328633713536</v>
+        <v>1.546909516036976e-06</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0005807155393995345</v>
+        <v>2.78476181847509e-05</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.00103259552270174</v>
+        <v>8.317852189065889e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.001248363638296723</v>
+        <v>9.980591130442917e-05</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0004832896811421961</v>
+        <v>8.210013220377732e-06</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0002305278612766415</v>
+        <v>3.034313340322115e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0001171511685242876</v>
+        <v>1.948445424204692e-05</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.000376773503376171</v>
+        <v>2.34263607126195e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0004659165279008448</v>
+        <v>4.057673504576087e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0003178826882503927</v>
+        <v>1.178261072709574e-06</v>
       </c>
       <c r="CE14" t="n">
-        <v>6.014472091919743e-05</v>
+        <v>1.465675632061902e-05</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0007004234939813614</v>
+        <v>3.709683733177371e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0003655343316495419</v>
+        <v>5.303511716192588e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0003351240884512663</v>
+        <v>1.537719799671322e-05</v>
       </c>
       <c r="CI14" t="n">
-        <v>4.984392944606952e-05</v>
+        <v>1.775076270860154e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0002352340234210715</v>
+        <v>2.777172994683497e-06</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0001768205547705293</v>
+        <v>6.006327566865366e-06</v>
       </c>
       <c r="CL14" t="n">
-        <v>6.132340058684349e-05</v>
+        <v>1.024621633405332e-05</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0009825477609410882</v>
+        <v>1.759863152983598e-06</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0008236478315666318</v>
+        <v>1.608836646482814e-05</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.780633465386927e-05</v>
+        <v>6.082762774894945e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0003929930098820478</v>
+        <v>9.478766878601164e-05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0002285032824147493</v>
+        <v>2.571220102254301e-05</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.000305788271361962</v>
+        <v>5.695691652363166e-05</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.000214299390790984</v>
+        <v>4.617720151145477e-06</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.001059880945831537</v>
+        <v>8.08096410764847e-06</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0002232005790574476</v>
+        <v>3.542286503943615e-05</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0002394314069533721</v>
+        <v>5.346458237909246e-06</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.000229482728173025</v>
+        <v>2.689532084332313e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0004642331041395664</v>
+        <v>3.178373663104139e-05</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.000405839120503515</v>
+        <v>4.66819983557798e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0001458048791391775</v>
+        <v>1.506243552285014e-05</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.162644886993803e-05</v>
+        <v>2.897980994021054e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002105302119161934</v>
+        <v>3.820943675236776e-06</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0001142617402365431</v>
+        <v>7.83535506343469e-06</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.551390232634731e-05</v>
+        <v>1.222420814883662e-05</v>
       </c>
       <c r="DE14" t="n">
-        <v>8.069344039540738e-05</v>
+        <v>4.098566932952963e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0009107223595492542</v>
+        <v>3.93508598790504e-05</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.000819950713776052</v>
+        <v>1.619207523617661e-06</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0002655238495208323</v>
+        <v>2.522789691283833e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0001158177401521243</v>
+        <v>1.617865927983075e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0002451590844430029</v>
+        <v>6.380485501722433e-06</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0008671774412505329</v>
+        <v>4.280119901522994e-05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0002516661770641804</v>
+        <v>5.548241097130813e-05</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.000287227361695841</v>
+        <v>5.941576091572642e-05</v>
       </c>
       <c r="DN14" t="n">
-        <v>2.635354758240283e-05</v>
+        <v>2.886183438022272e-06</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0006005583563819528</v>
+        <v>1.645419433771167e-05</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0004657107638195157</v>
+        <v>1.603796226845589e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.76882516220212e-05</v>
+        <v>1.320916908298386e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0009208928095176816</v>
+        <v>4.026188980787992e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.000384739541914314</v>
+        <v>1.184330358228181e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0003924164338968694</v>
+        <v>2.299741026945412e-05</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001353481638943776</v>
+        <v>2.073518407996744e-05</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0006486767088063061</v>
+        <v>3.693005055538379e-05</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0001973928592633456</v>
+        <v>5.071273335488513e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0008868408622220159</v>
+        <v>3.026269769179635e-05</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0002827206335496157</v>
+        <v>2.355071774218231e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.00017662147001829</v>
+        <v>7.546991128037916e-06</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0004324231122154742</v>
+        <v>2.597574166429695e-05</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.000594095850829035</v>
+        <v>2.583576497272588e-05</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.5028402635362e-05</v>
+        <v>1.300418989558239e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0001719928113743663</v>
+        <v>4.361866740509868e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>3.601855132728815e-05</v>
+        <v>2.003025110752787e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>2.699517244764138e-05</v>
+        <v>2.588302595540881e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0003040713490918279</v>
+        <v>2.05183205252979e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0007177659426815808</v>
+        <v>1.219030400534393e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0008410761947743595</v>
+        <v>6.341701373457909e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>1.045762383000692e-05</v>
+        <v>1.4337202628667e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>6.241200026124716e-06</v>
+        <v>2.997167030116543e-06</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.000284853857010603</v>
+        <v>1.057297140505398e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>8.849102596286684e-05</v>
+        <v>9.050801281773602e-07</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0002963391889352351</v>
+        <v>4.278235792298801e-06</v>
       </c>
       <c r="EO14" t="n">
-        <v>2.541033609304577e-05</v>
+        <v>4.3983773139189e-06</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0005958336405456066</v>
+        <v>2.416154893580824e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0003070450620725751</v>
+        <v>1.214638450619532e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0004067666013725102</v>
+        <v>3.63583312719129e-05</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0002109721972374246</v>
+        <v>1.427303141099401e-05</v>
       </c>
       <c r="ET14" t="n">
-        <v>9.774179488886148e-05</v>
+        <v>5.824453546665609e-05</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0003155407612212002</v>
+        <v>4.272375917935278e-06</v>
       </c>
       <c r="EV14" t="n">
-        <v>1.3315071555553e-05</v>
+        <v>3.776823723455891e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0003410975623410195</v>
+        <v>7.261677637870889e-06</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.000243998336372897</v>
+        <v>5.432148100226186e-07</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0002914717770181596</v>
+        <v>2.055114600807428e-05</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0006130626425147057</v>
+        <v>3.642231240519322e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0003907536738552153</v>
+        <v>6.351586489472538e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0001977596548385918</v>
+        <v>1.405094008077867e-05</v>
       </c>
       <c r="FC14" t="n">
-        <v>8.900729881133884e-06</v>
+        <v>2.357304765610024e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001807493099477142</v>
+        <v>5.186601811146829e-06</v>
       </c>
       <c r="FE14" t="n">
-        <v>9.517658327240497e-05</v>
+        <v>2.17209762922721e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0001608886668691412</v>
+        <v>1.45528138091322e-05</v>
       </c>
       <c r="FG14" t="n">
-        <v>9.298199438489974e-05</v>
+        <v>1.398306812916417e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0004095019539818168</v>
+        <v>2.208485602750443e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>1.380120556859765e-05</v>
+        <v>8.013086699065752e-06</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0004054601886309683</v>
+        <v>2.634986776683945e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0002826677518896759</v>
+        <v>8.841501767165028e-06</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0003187778347637504</v>
+        <v>3.385278978385031e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0001936134358402342</v>
+        <v>8.276451808342244e-06</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0004320171719882637</v>
+        <v>1.102314490708522e-05</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0002905826841015369</v>
+        <v>5.018142474000342e-06</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0004354143457021564</v>
+        <v>8.164264727383852e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0002307973627466708</v>
+        <v>1.836224691942334e-05</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0006244128453545272</v>
+        <v>2.812497041304596e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>5.568485357798636e-05</v>
+        <v>1.278006038774038e-05</v>
       </c>
       <c r="FT14" t="n">
-        <v>4.509325663093477e-05</v>
+        <v>7.352170359808952e-05</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0003437700506765395</v>
+        <v>2.865882379410323e-05</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001237188844243065</v>
+        <v>2.626672358019277e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.000308311078697443</v>
+        <v>3.693263352033682e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.000107096871943213</v>
+        <v>1.858088035078254e-05</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.000135502777993679</v>
+        <v>3.106497752014548e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0005420373636297882</v>
+        <v>2.308529656147584e-05</v>
       </c>
       <c r="GA14" t="n">
-        <v>9.501620661467314e-05</v>
+        <v>1.095524567062967e-05</v>
       </c>
       <c r="GB14" t="n">
-        <v>4.416062438394874e-06</v>
+        <v>6.206709804246202e-05</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0005632381653413177</v>
+        <v>1.388840155414073e-05</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0008309768163599074</v>
+        <v>3.829242268693633e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0002630728995427489</v>
+        <v>8.581333531765267e-06</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001499563513789326</v>
+        <v>2.458778544678353e-05</v>
       </c>
       <c r="GG14" t="n">
-        <v>2.216751818195917e-05</v>
+        <v>4.33377645094879e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5.99786017119186e-06</v>
+        <v>2.820008376147598e-06</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0001210503105539829</v>
+        <v>1.501924452895764e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>1.985249036806636e-05</v>
+        <v>2.000200311158551e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>4.851119956583716e-05</v>
+        <v>5.65989194001304e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>5.99705490458291e-05</v>
+        <v>6.623610261158319e-06</v>
       </c>
       <c r="F15" t="n">
-        <v>5.99590057390742e-05</v>
+        <v>1.551083187223412e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>2.350299109821208e-05</v>
+        <v>3.45855914929416e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>2.821531234076247e-05</v>
+        <v>1.946955853782129e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>9.561234037391841e-06</v>
+        <v>2.114098833772005e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>1.15713646664517e-05</v>
+        <v>6.891664270369802e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>9.425223834114149e-05</v>
+        <v>2.192974898207467e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>3.524062094584224e-06</v>
+        <v>1.878345074146637e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>3.06061738228891e-05</v>
+        <v>1.162763328466099e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.385720967547968e-05</v>
+        <v>1.095031439035665e-05</v>
       </c>
       <c r="O15" t="n">
-        <v>5.345715180737898e-05</v>
+        <v>1.451306707167532e-05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.537144064262975e-05</v>
+        <v>6.08816162639414e-06</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.556904968922026e-06</v>
+        <v>1.116858402383514e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>8.909118150768336e-06</v>
+        <v>2.164533270843094e-06</v>
       </c>
       <c r="S15" t="n">
-        <v>8.957767363426683e-07</v>
+        <v>3.049495262530399e-06</v>
       </c>
       <c r="T15" t="n">
-        <v>1.708003583189566e-05</v>
+        <v>3.223383600925445e-06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.826865511451615e-06</v>
+        <v>1.374986254631949e-06</v>
       </c>
       <c r="V15" t="n">
-        <v>2.217849578300957e-05</v>
+        <v>1.095440666176728e-06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.722491288091987e-05</v>
+        <v>8.390696848437074e-08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.863746183516923e-05</v>
+        <v>1.956051391971414e-06</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.268486231419956e-06</v>
+        <v>4.076488949067425e-06</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.6638012311887e-05</v>
+        <v>6.140078312455444e-07</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.982203664549161e-06</v>
+        <v>3.163972905895207e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.672882929909974e-06</v>
+        <v>6.660404324065894e-06</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.362447073915973e-05</v>
+        <v>3.639767328422749e-06</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1707692212658e-06</v>
+        <v>2.952680461021373e-06</v>
       </c>
       <c r="AE15" t="n">
-        <v>8.614036232756916e-06</v>
+        <v>2.760856432360015e-06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.512737071607262e-06</v>
+        <v>8.960117156675551e-06</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.681379778048722e-06</v>
+        <v>2.963019824164803e-06</v>
       </c>
       <c r="AH15" t="n">
-        <v>9.081031748792157e-06</v>
+        <v>3.990094228356611e-07</v>
       </c>
       <c r="AI15" t="n">
-        <v>8.091428753687069e-06</v>
+        <v>4.92102208227152e-06</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.920727860735497e-06</v>
+        <v>2.534400891818223e-06</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.245277962880209e-05</v>
+        <v>2.169974095522775e-06</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.221997783635743e-05</v>
+        <v>9.726550160849001e-07</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.563771886343602e-06</v>
+        <v>4.718174295703648e-07</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.894257578300312e-06</v>
+        <v>1.018639181893377e-06</v>
       </c>
       <c r="AO15" t="n">
-        <v>3.859800017380621e-06</v>
+        <v>7.117372661014087e-06</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.335721364943311e-05</v>
+        <v>4.387471562949941e-06</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.003376837616088e-06</v>
+        <v>4.240107955411077e-06</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.099936980608618e-05</v>
+        <v>5.299601525621256e-06</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.406978662998881e-05</v>
+        <v>4.133318725507706e-06</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.337956049013883e-06</v>
+        <v>1.370254949506489e-06</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.235047425841913e-05</v>
+        <v>2.512751598260365e-05</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.251908088306664e-05</v>
+        <v>7.030394044704735e-08</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.714693204732612e-06</v>
+        <v>2.686279913177714e-06</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.00087160919793e-05</v>
+        <v>1.051206982083386e-05</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.587641549529508e-05</v>
+        <v>1.492365845479071e-05</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.736048716338701e-06</v>
+        <v>1.622139734536177e-06</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.80827992153354e-05</v>
+        <v>3.444735739321914e-06</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.518105798633769e-06</v>
+        <v>7.449785698554479e-06</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.679400485154474e-06</v>
+        <v>1.171397912003158e-06</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.942867675097659e-05</v>
+        <v>1.8020318748313e-06</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.146295082638972e-05</v>
+        <v>7.496131502193748e-07</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.443008113710675e-05</v>
+        <v>2.085956793962396e-06</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.419406468514353e-05</v>
+        <v>2.936648115792195e-06</v>
       </c>
       <c r="BH15" t="n">
-        <v>1.164966852229554e-05</v>
+        <v>7.481095849470876e-07</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.768121910572518e-05</v>
+        <v>2.752242153292173e-06</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.925318065332249e-05</v>
+        <v>1.158948634838453e-05</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.859113454993349e-06</v>
+        <v>1.615713244973449e-06</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.097332824429031e-05</v>
+        <v>1.234632577507e-06</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.879385465348605e-05</v>
+        <v>8.56266706250608e-06</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.285343296331121e-05</v>
+        <v>2.599764684418915e-06</v>
       </c>
       <c r="BO15" t="n">
-        <v>7.834205462131649e-06</v>
+        <v>5.454072834254475e-06</v>
       </c>
       <c r="BP15" t="n">
-        <v>2.273137170050177e-06</v>
+        <v>9.764075912244152e-06</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.656017598696053e-06</v>
+        <v>3.596743681555381e-06</v>
       </c>
       <c r="BR15" t="n">
-        <v>4.705586434283759e-06</v>
+        <v>1.83980318979593e-06</v>
       </c>
       <c r="BS15" t="n">
-        <v>5.951725142949726e-06</v>
+        <v>2.654201125551481e-07</v>
       </c>
       <c r="BT15" t="n">
-        <v>9.168913493340369e-06</v>
+        <v>2.678479859241634e-06</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.703675353492144e-06</v>
+        <v>4.881116183241829e-06</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.076784873381257e-05</v>
+        <v>1.098684333555866e-05</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.474816392350476e-05</v>
+        <v>7.020809107416426e-07</v>
       </c>
       <c r="BX15" t="n">
-        <v>1.113477264880203e-05</v>
+        <v>1.646340024308302e-06</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.577339753566775e-05</v>
+        <v>1.465861032556859e-06</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.891796379524749e-06</v>
+        <v>3.10607310893829e-06</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.764526915503666e-06</v>
+        <v>5.445352144306526e-06</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.685876203642692e-06</v>
+        <v>3.101925813098205e-06</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.051495837600669e-05</v>
+        <v>3.420341045057285e-06</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.33011643710779e-08</v>
+        <v>7.07156118551211e-07</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.869632615125738e-05</v>
+        <v>3.900501269527012e-06</v>
       </c>
       <c r="CF15" t="n">
-        <v>7.360177733062301e-06</v>
+        <v>6.291472232078377e-08</v>
       </c>
       <c r="CG15" t="n">
-        <v>8.03492366685532e-06</v>
+        <v>4.505932906795351e-07</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.908392164295947e-07</v>
+        <v>5.045823854743503e-06</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.136659011535812e-05</v>
+        <v>2.753663920884719e-06</v>
       </c>
       <c r="CJ15" t="n">
-        <v>4.879997050011298e-06</v>
+        <v>9.974911563404021e-07</v>
       </c>
       <c r="CK15" t="n">
-        <v>4.150319000473246e-06</v>
+        <v>1.102603619074216e-06</v>
       </c>
       <c r="CL15" t="n">
-        <v>5.830835107190069e-06</v>
+        <v>2.211531295870373e-07</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.902221265481785e-05</v>
+        <v>3.388777713553282e-06</v>
       </c>
       <c r="CN15" t="n">
-        <v>7.190580618043896e-06</v>
+        <v>1.226491804118268e-05</v>
       </c>
       <c r="CO15" t="n">
-        <v>5.703848728444427e-06</v>
+        <v>3.491870756988646e-06</v>
       </c>
       <c r="CP15" t="n">
-        <v>6.001099791319575e-06</v>
+        <v>1.075182353815762e-06</v>
       </c>
       <c r="CQ15" t="n">
-        <v>1.190149032481713e-05</v>
+        <v>8.334308404300828e-06</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.00989309430588e-05</v>
+        <v>2.072724782919977e-06</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.205769851570949e-05</v>
+        <v>1.268221240025014e-06</v>
       </c>
       <c r="CT15" t="n">
-        <v>1.772862560756039e-05</v>
+        <v>2.176391035391134e-06</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.520919568065437e-06</v>
+        <v>1.022293645291938e-06</v>
       </c>
       <c r="CV15" t="n">
-        <v>3.331754214741522e-07</v>
+        <v>3.727633384187357e-07</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.57350477820728e-05</v>
+        <v>4.267047643224942e-06</v>
       </c>
       <c r="CX15" t="n">
-        <v>8.420531230513006e-06</v>
+        <v>7.348609187829425e-07</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.27651946968399e-05</v>
+        <v>1.404047907271888e-06</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.852504283306189e-06</v>
+        <v>2.70377586275572e-06</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.579371746629477e-05</v>
+        <v>3.274489245086443e-06</v>
       </c>
       <c r="DB15" t="n">
-        <v>3.112233571300749e-06</v>
+        <v>2.382241063969559e-06</v>
       </c>
       <c r="DC15" t="n">
-        <v>7.459331754944287e-06</v>
+        <v>2.511306433916616e-07</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.462197133150767e-06</v>
+        <v>3.54954920567252e-07</v>
       </c>
       <c r="DE15" t="n">
-        <v>4.726956831291318e-06</v>
+        <v>2.321797865079134e-07</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.462342126818839e-05</v>
+        <v>7.63554544391809e-06</v>
       </c>
       <c r="DG15" t="n">
-        <v>4.535534117167117e-06</v>
+        <v>5.890164175070822e-06</v>
       </c>
       <c r="DH15" t="n">
-        <v>3.206069231964648e-05</v>
+        <v>2.196413106503314e-06</v>
       </c>
       <c r="DI15" t="n">
-        <v>7.966709745232947e-06</v>
+        <v>3.075803078900208e-06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.281285671619116e-06</v>
+        <v>7.269149136845954e-06</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.93261839740444e-05</v>
+        <v>2.551528041294659e-06</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.305141449847724e-05</v>
+        <v>3.896832822647411e-06</v>
       </c>
       <c r="DM15" t="n">
-        <v>1.177073045255383e-05</v>
+        <v>6.838100489403587e-06</v>
       </c>
       <c r="DN15" t="n">
-        <v>5.026999133406207e-06</v>
+        <v>4.047645916216425e-07</v>
       </c>
       <c r="DO15" t="n">
-        <v>7.914016350696329e-06</v>
+        <v>2.547336862335214e-06</v>
       </c>
       <c r="DP15" t="n">
-        <v>1.647102408242063e-06</v>
+        <v>2.035333750427526e-07</v>
       </c>
       <c r="DQ15" t="n">
-        <v>3.618323944465374e-06</v>
+        <v>8.276578228105791e-06</v>
       </c>
       <c r="DR15" t="n">
-        <v>2.525655872887e-06</v>
+        <v>1.091463445845875e-06</v>
       </c>
       <c r="DS15" t="n">
-        <v>1.193718890135642e-05</v>
+        <v>3.640914655989036e-06</v>
       </c>
       <c r="DT15" t="n">
-        <v>5.891160526516614e-06</v>
+        <v>1.100257577490993e-06</v>
       </c>
       <c r="DU15" t="n">
-        <v>7.634464054717682e-06</v>
+        <v>9.894781669572694e-07</v>
       </c>
       <c r="DV15" t="n">
-        <v>6.310720436886186e-06</v>
+        <v>4.945366526953876e-06</v>
       </c>
       <c r="DW15" t="n">
-        <v>3.048755843337858e-06</v>
+        <v>2.77803155768197e-06</v>
       </c>
       <c r="DX15" t="n">
-        <v>2.338362946829875e-06</v>
+        <v>2.613888455016422e-06</v>
       </c>
       <c r="DY15" t="n">
-        <v>1.289136616833275e-05</v>
+        <v>2.152309434677591e-06</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.322751586485538e-06</v>
+        <v>2.9435118449328e-06</v>
       </c>
       <c r="EA15" t="n">
-        <v>5.04848458149354e-06</v>
+        <v>9.960127499653026e-06</v>
       </c>
       <c r="EB15" t="n">
-        <v>4.525616532191634e-06</v>
+        <v>3.137220573989907e-06</v>
       </c>
       <c r="EC15" t="n">
-        <v>8.512369049640256e-07</v>
+        <v>6.319833687484788e-07</v>
       </c>
       <c r="ED15" t="n">
-        <v>8.572059414291289e-06</v>
+        <v>7.277817076101201e-06</v>
       </c>
       <c r="EE15" t="n">
-        <v>6.937707439647056e-07</v>
+        <v>4.850830464420142e-06</v>
       </c>
       <c r="EF15" t="n">
-        <v>5.773405973741319e-06</v>
+        <v>3.361204790053307e-07</v>
       </c>
       <c r="EG15" t="n">
-        <v>1.540171251690481e-05</v>
+        <v>4.297627640426072e-07</v>
       </c>
       <c r="EH15" t="n">
-        <v>9.544208296574652e-06</v>
+        <v>6.3246682202589e-07</v>
       </c>
       <c r="EI15" t="n">
-        <v>2.803829374897759e-06</v>
+        <v>1.059133774106158e-05</v>
       </c>
       <c r="EJ15" t="n">
-        <v>8.28500105853891e-06</v>
+        <v>4.775668571710412e-07</v>
       </c>
       <c r="EK15" t="n">
-        <v>8.511537089361809e-06</v>
+        <v>2.915665390901268e-06</v>
       </c>
       <c r="EL15" t="n">
-        <v>5.96288464294048e-06</v>
+        <v>4.492935659072828e-07</v>
       </c>
       <c r="EM15" t="n">
-        <v>2.707903831833391e-06</v>
+        <v>1.734794977892307e-06</v>
       </c>
       <c r="EN15" t="n">
-        <v>6.714560640830314e-08</v>
+        <v>3.041206468878954e-07</v>
       </c>
       <c r="EO15" t="n">
-        <v>5.163519745110534e-06</v>
+        <v>1.551955620016088e-06</v>
       </c>
       <c r="EP15" t="n">
-        <v>8.14022496342659e-06</v>
+        <v>1.045700514623604e-06</v>
       </c>
       <c r="EQ15" t="n">
-        <v>1.370988411508733e-05</v>
+        <v>1.149768650066108e-06</v>
       </c>
       <c r="ER15" t="n">
-        <v>1.606374280527234e-05</v>
+        <v>3.791531298702466e-06</v>
       </c>
       <c r="ES15" t="n">
-        <v>9.645586942497175e-06</v>
+        <v>4.326055204728618e-06</v>
       </c>
       <c r="ET15" t="n">
-        <v>1.535720366518945e-05</v>
+        <v>5.257423708826536e-06</v>
       </c>
       <c r="EU15" t="n">
-        <v>6.501652933366131e-06</v>
+        <v>3.670025080282358e-06</v>
       </c>
       <c r="EV15" t="n">
-        <v>1.951166268554516e-05</v>
+        <v>1.120768502005376e-06</v>
       </c>
       <c r="EW15" t="n">
-        <v>2.271710400236771e-06</v>
+        <v>1.556538791191997e-06</v>
       </c>
       <c r="EX15" t="n">
-        <v>1.790878741303459e-06</v>
+        <v>3.70524844583997e-07</v>
       </c>
       <c r="EY15" t="n">
-        <v>1.46308357216185e-05</v>
+        <v>4.847322088608053e-06</v>
       </c>
       <c r="EZ15" t="n">
-        <v>5.551692993321922e-06</v>
+        <v>3.261174867930094e-07</v>
       </c>
       <c r="FA15" t="n">
-        <v>1.215464271808742e-05</v>
+        <v>4.821288257517153e-07</v>
       </c>
       <c r="FB15" t="n">
-        <v>2.924494765466079e-06</v>
+        <v>3.833007212961093e-06</v>
       </c>
       <c r="FC15" t="n">
-        <v>1.222731953021139e-05</v>
+        <v>2.694489467103267e-06</v>
       </c>
       <c r="FD15" t="n">
-        <v>7.215533969429089e-06</v>
+        <v>6.720023293382837e-07</v>
       </c>
       <c r="FE15" t="n">
-        <v>6.210501851455774e-06</v>
+        <v>1.988077826808876e-07</v>
       </c>
       <c r="FF15" t="n">
-        <v>6.7107830545865e-06</v>
+        <v>9.005345305013179e-07</v>
       </c>
       <c r="FG15" t="n">
-        <v>6.739264790667221e-06</v>
+        <v>1.03980028143269e-06</v>
       </c>
       <c r="FH15" t="n">
-        <v>1.061777220456861e-05</v>
+        <v>2.31889248425432e-06</v>
       </c>
       <c r="FI15" t="n">
-        <v>8.46879538585199e-06</v>
+        <v>5.253381232250831e-07</v>
       </c>
       <c r="FJ15" t="n">
-        <v>1.66459667525487e-05</v>
+        <v>4.731484295916744e-06</v>
       </c>
       <c r="FK15" t="n">
-        <v>4.931749117531581e-06</v>
+        <v>4.40629310105578e-06</v>
       </c>
       <c r="FL15" t="n">
-        <v>9.084741577680688e-06</v>
+        <v>5.912025926591014e-07</v>
       </c>
       <c r="FM15" t="n">
-        <v>3.594415375118842e-06</v>
+        <v>2.14779720408842e-06</v>
       </c>
       <c r="FN15" t="n">
-        <v>8.135753887472674e-06</v>
+        <v>6.353175194817595e-07</v>
       </c>
       <c r="FO15" t="n">
-        <v>8.220767085731495e-06</v>
+        <v>8.28431893751258e-06</v>
       </c>
       <c r="FP15" t="n">
-        <v>2.534372470108792e-06</v>
+        <v>1.903517841128632e-07</v>
       </c>
       <c r="FQ15" t="n">
-        <v>4.386961336422246e-06</v>
+        <v>1.559872544021346e-06</v>
       </c>
       <c r="FR15" t="n">
-        <v>1.104487273551058e-05</v>
+        <v>2.927699824795127e-07</v>
       </c>
       <c r="FS15" t="n">
-        <v>1.957268614205532e-05</v>
+        <v>7.282102160388604e-06</v>
       </c>
       <c r="FT15" t="n">
-        <v>9.523603694105987e-06</v>
+        <v>9.90222815744346e-06</v>
       </c>
       <c r="FU15" t="n">
-        <v>1.945634039657307e-06</v>
+        <v>5.812241397507023e-06</v>
       </c>
       <c r="FV15" t="n">
-        <v>8.538063411833718e-06</v>
+        <v>9.544737622491084e-06</v>
       </c>
       <c r="FW15" t="n">
-        <v>6.747131919837557e-06</v>
+        <v>1.290506952500436e-05</v>
       </c>
       <c r="FX15" t="n">
-        <v>8.983845418697456e-07</v>
+        <v>3.934900632884819e-06</v>
       </c>
       <c r="FY15" t="n">
-        <v>2.253436468890868e-05</v>
+        <v>3.43157580573461e-06</v>
       </c>
       <c r="FZ15" t="n">
-        <v>8.484075806336477e-07</v>
+        <v>2.448884515615646e-06</v>
       </c>
       <c r="GA15" t="n">
-        <v>4.361500941740815e-06</v>
+        <v>2.975149300254998e-06</v>
       </c>
       <c r="GB15" t="n">
-        <v>1.153936864284333e-05</v>
+        <v>1.714841118882759e-06</v>
       </c>
       <c r="GC15" t="n">
-        <v>1.167244045063853e-05</v>
+        <v>1.792594730432029e-07</v>
       </c>
       <c r="GD15" t="n">
-        <v>1.639102265471593e-05</v>
+        <v>2.458803919580532e-06</v>
       </c>
       <c r="GE15" t="n">
-        <v>4.67333520646207e-05</v>
+        <v>4.75497745355824e-06</v>
       </c>
       <c r="GF15" t="n">
-        <v>5.13345639774343e-07</v>
+        <v>3.715263574122218e-06</v>
       </c>
       <c r="GG15" t="n">
-        <v>1.356988605039078e-06</v>
+        <v>2.708704016640695e-07</v>
       </c>
     </row>
   </sheetData>
